--- a/Main Data - Figures 1 to 4.xlsx
+++ b/Main Data - Figures 1 to 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/istaffel_ic_ac_uk/Documents/Nathan &amp; Iain Folder/~ Wedges paper/Code and Data - Submission 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/istaffel_ic_ac_uk/Documents/Nathan &amp; Iain Folder/~ Wedges paper/Submission 3 - Science/(corrected submission files)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{17787BCD-F3D9-4239-B019-6415FC27D6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A6A8270-F698-487A-B8C4-1A66ADCEEEC1}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{17787BCD-F3D9-4239-B019-6415FC27D6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CE41535-1D70-48E9-9EE6-94C55805F594}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="-120" windowWidth="28065" windowHeight="16440" xr2:uid="{14C3A848-E55B-4CE3-AACB-8601D1D1106B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" activeTab="2" xr2:uid="{14C3A848-E55B-4CE3-AACB-8601D1D1106B}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
@@ -1354,7 +1354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1396,37 +1396,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1437,57 +1424,60 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1820,45 +1810,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1E96C4-3534-40E9-A7A7-72F699F931FB}">
   <dimension ref="B1:N80"/>
-  <sheetFormatPr defaultColWidth="4.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="4.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C5" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C7" s="15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C15" s="7" t="s">
         <v>0</v>
       </c>
@@ -1866,7 +1856,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C16" s="7" t="s">
         <v>94</v>
       </c>
@@ -1874,7 +1864,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C17" s="7" t="s">
         <v>95</v>
       </c>
@@ -1882,7 +1872,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C18" s="7" t="s">
         <v>92</v>
       </c>
@@ -1890,7 +1880,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C19" s="7" t="s">
         <v>2</v>
       </c>
@@ -1898,7 +1888,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C20" s="7" t="s">
         <v>3</v>
       </c>
@@ -1906,7 +1896,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C21" s="7" t="s">
         <v>4</v>
       </c>
@@ -1914,7 +1904,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C22" s="7" t="s">
         <v>5</v>
       </c>
@@ -1922,7 +1912,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C23" s="7" t="s">
         <v>6</v>
       </c>
@@ -1930,7 +1920,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C24" s="7" t="s">
         <v>7</v>
       </c>
@@ -1938,12 +1928,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C30" s="7" t="s">
         <v>57</v>
       </c>
@@ -1951,7 +1941,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C31" s="7" t="s">
         <v>64</v>
       </c>
@@ -1959,7 +1949,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C32" s="7" t="s">
         <v>164</v>
       </c>
@@ -1967,7 +1957,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C33" s="7" t="s">
         <v>266</v>
       </c>
@@ -1975,7 +1965,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C34" s="7" t="s">
         <v>265</v>
       </c>
@@ -1983,7 +1973,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C35" s="7" t="s">
         <v>184</v>
       </c>
@@ -1991,7 +1981,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C36" s="7" t="s">
         <v>264</v>
       </c>
@@ -1999,7 +1989,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C37" s="7" t="s">
         <v>263</v>
       </c>
@@ -2007,7 +1997,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C38" s="7" t="s">
         <v>262</v>
       </c>
@@ -2015,7 +2005,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C39" s="7" t="s">
         <v>261</v>
       </c>
@@ -2023,7 +2013,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C40" s="7" t="s">
         <v>260</v>
       </c>
@@ -2031,7 +2021,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C41" s="7" t="s">
         <v>259</v>
       </c>
@@ -2039,7 +2029,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C42" s="7" t="s">
         <v>258</v>
       </c>
@@ -2047,7 +2037,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C43" s="7" t="s">
         <v>257</v>
       </c>
@@ -2055,7 +2045,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C44" s="7" t="s">
         <v>256</v>
       </c>
@@ -2063,7 +2053,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="45" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C45" s="7" t="s">
         <v>255</v>
       </c>
@@ -2071,7 +2061,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="46" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C46" s="7" t="s">
         <v>254</v>
       </c>
@@ -2079,7 +2069,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="47" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C47" s="7" t="s">
         <v>253</v>
       </c>
@@ -2087,7 +2077,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="48" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C48" s="7" t="s">
         <v>252</v>
       </c>
@@ -2095,7 +2085,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C49" s="7" t="s">
         <v>251</v>
       </c>
@@ -2103,7 +2093,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C50" s="7" t="s">
         <v>250</v>
       </c>
@@ -2111,7 +2101,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C51" s="7" t="s">
         <v>249</v>
       </c>
@@ -2119,7 +2109,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C52" s="7" t="s">
         <v>248</v>
       </c>
@@ -2127,32 +2117,32 @@
         <v>287</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" s="7" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C57" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C62" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C63" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C65" s="7" t="s">
         <v>65</v>
       </c>
@@ -2160,7 +2150,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C66" s="7" t="s">
         <v>57</v>
       </c>
@@ -2168,7 +2158,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C67" s="7" t="s">
         <v>64</v>
       </c>
@@ -2176,7 +2166,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="68" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C68" s="7" t="s">
         <v>56</v>
       </c>
@@ -2184,7 +2174,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C69" s="7" t="s">
         <v>74</v>
       </c>
@@ -2192,7 +2182,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C70" s="7" t="s">
         <v>58</v>
       </c>
@@ -2200,7 +2190,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C71" s="7" t="s">
         <v>59</v>
       </c>
@@ -2208,7 +2198,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="72" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C72" s="7" t="s">
         <v>60</v>
       </c>
@@ -2216,7 +2206,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="73" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C73" s="7" t="s">
         <v>61</v>
       </c>
@@ -2224,7 +2214,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C74" s="7" t="s">
         <v>62</v>
       </c>
@@ -2232,7 +2222,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="75" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C75" s="7" t="s">
         <v>63</v>
       </c>
@@ -2240,7 +2230,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C76" s="7" t="s">
         <v>85</v>
       </c>
@@ -2248,7 +2238,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="77" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C77" s="7" t="s">
         <v>84</v>
       </c>
@@ -2256,7 +2246,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="78" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C78" s="7" t="s">
         <v>86</v>
       </c>
@@ -2264,7 +2254,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C79" s="7" t="s">
         <v>88</v>
       </c>
@@ -2272,7 +2262,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C80" s="7" t="s">
         <v>87</v>
       </c>
@@ -2288,12 +2278,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A67AAD-373C-40D4-962B-69BDBB12ACBE}">
   <dimension ref="A1:J52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="10" width="11.42578125" customWidth="1"/>
+    <col min="1" max="10" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2325,7 +2315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -2358,7 +2348,7 @@
         <v>4.0514633964181401</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2392,7 +2382,7 @@
         <v>3.9951026720705598</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2426,7 +2416,7 @@
         <v>3.9361526892694498</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -2460,7 +2450,7 @@
         <v>3.8739548345705801</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -2494,7 +2484,7 @@
         <v>3.8080100724836901</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -2528,7 +2518,7 @@
         <v>3.7380218627958501</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -2562,7 +2552,7 @@
         <v>3.6638964451684601</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -2596,7 +2586,7 @@
         <v>3.5857565901325201</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -2630,7 +2620,7 @@
         <v>3.5039306073100298</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2664,7 +2654,7 @@
         <v>3.4188770567767</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -2698,7 +2688,7 @@
         <v>3.33112801282534</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -2732,7 +2722,7 @@
         <v>3.2413153198700999</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -2766,7 +2756,7 @@
         <v>3.1501387390080802</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2800,7 +2790,7 @@
         <v>3.0583061708524601</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2834,7 +2824,7 @@
         <v>2.9665063528542599</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2868,7 +2858,7 @@
         <v>2.8753745923750902</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2902,7 +2892,7 @@
         <v>2.7854542748457001</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2936,7 +2926,7 @@
         <v>2.6971854848313801</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2970,7 +2960,7 @@
         <v>2.6109203649184001</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3004,7 +2994,7 @@
         <v>2.52696280263691</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3038,7 +3028,7 @@
         <v>2.4456031060632801</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -3072,7 +3062,7 @@
         <v>2.36715658395046</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -3106,7 +3096,7 @@
         <v>2.2919941051935799</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -3140,7 +3130,7 @@
         <v>2.2205437757291602</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -3174,7 +3164,7 @@
         <v>2.1532752644328701</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -3208,7 +3198,7 @@
         <v>2.09066244282088</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -3242,7 +3232,7 @@
         <v>2.0331270246207498</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -3276,7 +3266,7 @@
         <v>1.9809638038967801</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -3310,7 +3300,7 @@
         <v>1.9342747759955701</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -3344,7 +3334,7 @@
         <v>1.8929322641561801</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -3378,7 +3368,7 @@
         <v>1.8565500813920801</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -3412,7 +3402,7 @@
         <v>1.82446525426518</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -3446,7 +3436,7 @@
         <v>1.79575504262826</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -3480,7 +3470,7 @@
         <v>1.76937086453822</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -3514,7 +3504,7 @@
         <v>1.7442915385404201</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -3548,7 +3538,7 @@
         <v>1.71966301833681</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -3582,7 +3572,7 @@
         <v>1.69488759632813</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -3616,7 +3606,7 @@
         <v>1.6697114227085399</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -3650,7 +3640,7 @@
         <v>1.6442522470185901</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -3684,7 +3674,7 @@
         <v>1.6188881322625699</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -3718,7 +3708,7 @@
         <v>1.5941470725876601</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -3752,7 +3742,7 @@
         <v>1.5706189020694401</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -3786,7 +3776,7 @@
         <v>1.5488497470406799</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -3820,7 +3810,7 @@
         <v>1.52925811659452</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -3854,7 +3844,7 @@
         <v>1.5120981309339601</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -3888,7 +3878,7 @@
         <v>1.4974272984494299</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -3922,7 +3912,7 @@
         <v>1.4851415962405099</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -3956,7 +3946,7 @@
         <v>1.4750137279439299</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -3990,7 +3980,7 @@
         <v>1.4667228299458499</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -4024,7 +4014,7 @@
         <v>1.4599164027966001</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -4066,21 +4056,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6E2DE1-C104-4E53-9B03-CEC9DC9FDCFA}">
   <dimension ref="A1:Y61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="13.28515625" style="17" customWidth="1"/>
-    <col min="10" max="12" width="12.140625" style="17" customWidth="1"/>
-    <col min="13" max="23" width="13.7109375" style="17" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13.26953125" customWidth="1"/>
+    <col min="10" max="12" width="12.1796875" customWidth="1"/>
+    <col min="13" max="23" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>57</v>
       </c>
@@ -4151,3284 +4140,3278 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>239</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" t="s">
         <v>247</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" t="s">
         <v>237</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="42">
         <f>D2/Fig2Fig3Context!$F$6</f>
         <v>0</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G2" s="49">
-        <f>AVERAGE(M2:P2)</f>
+      <c r="G2" s="43">
+        <f t="shared" ref="G2:G18" si="0">AVERAGE(M2:P2)</f>
         <v>1957.0387500000002</v>
       </c>
-      <c r="H2" s="49">
-        <f>MAX(M2:P2)</f>
+      <c r="H2" s="43">
+        <f t="shared" ref="H2:H18" si="1">MAX(M2:P2)</f>
         <v>2061.3690000000001</v>
       </c>
-      <c r="I2" s="49">
-        <f>MIN(M2:P2)</f>
+      <c r="I2" s="43">
+        <f t="shared" ref="I2:I18" si="2">MIN(M2:P2)</f>
         <v>1812.2550000000001</v>
       </c>
-      <c r="J2" s="50">
-        <f>AVERAGE(Q2:T2)</f>
+      <c r="J2" s="44">
+        <f t="shared" ref="J2:J18" si="3">AVERAGE(Q2:T2)</f>
         <v>4.5478124132952477E-2</v>
       </c>
-      <c r="K2" s="50">
-        <f>MAX(Q2:T2)</f>
+      <c r="K2" s="44">
+        <f t="shared" ref="K2:K18" si="4">MAX(Q2:T2)</f>
         <v>5.9913561716770806E-2</v>
       </c>
-      <c r="L2" s="50">
-        <f>MIN(Q2:T2)</f>
+      <c r="L2" s="44">
+        <f t="shared" ref="L2:L18" si="5">MIN(Q2:T2)</f>
         <v>2.9411389968340289E-2</v>
       </c>
-      <c r="M2" s="49">
+      <c r="M2" s="43">
         <v>1957.048</v>
       </c>
-      <c r="N2" s="49">
+      <c r="N2" s="43">
         <v>1997.4829999999999</v>
       </c>
-      <c r="O2" s="49">
+      <c r="O2" s="43">
         <v>1812.2550000000001</v>
       </c>
-      <c r="P2" s="49">
+      <c r="P2" s="43">
         <v>2061.3690000000001</v>
       </c>
-      <c r="Q2" s="51">
+      <c r="Q2" s="45">
         <f>M2/Fig2Fig3Context!F$41</f>
         <v>4.4646882143188571E-2</v>
       </c>
-      <c r="R2" s="51">
+      <c r="R2" s="45">
         <f>N2/Fig2Fig3Context!G$41</f>
         <v>4.7940662703510231E-2</v>
       </c>
-      <c r="S2" s="51">
+      <c r="S2" s="45">
         <f>O2/Fig2Fig3Context!H$41</f>
         <v>2.9411389968340289E-2</v>
       </c>
-      <c r="T2" s="51">
+      <c r="T2" s="45">
         <f>P2/Fig2Fig3Context!I$41</f>
         <v>5.9913561716770806E-2</v>
       </c>
-      <c r="U2" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V2" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W2" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="U2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>239</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="48">
+      <c r="E3" s="42">
         <f>D3/Fig2Fig3Context!$F$6</f>
         <v>0</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G3" s="49">
-        <f>AVERAGE(M3:P3)</f>
+      <c r="G3" s="43">
+        <f t="shared" si="0"/>
         <v>1573.4222499999998</v>
       </c>
-      <c r="H3" s="49">
-        <f>MAX(M3:P3)</f>
+      <c r="H3" s="43">
+        <f t="shared" si="1"/>
         <v>1640.7539999999999</v>
       </c>
-      <c r="I3" s="49">
-        <f>MIN(M3:P3)</f>
+      <c r="I3" s="43">
+        <f t="shared" si="2"/>
         <v>1478.94</v>
       </c>
-      <c r="J3" s="50">
-        <f>AVERAGE(Q3:T3)</f>
+      <c r="J3" s="44">
+        <f t="shared" si="3"/>
         <v>3.6499852422391878E-2</v>
       </c>
-      <c r="K3" s="50">
-        <f>MAX(Q3:T3)</f>
+      <c r="K3" s="44">
+        <f t="shared" si="4"/>
         <v>4.7688412914445956E-2</v>
       </c>
-      <c r="L3" s="50">
-        <f>MIN(Q3:T3)</f>
+      <c r="L3" s="44">
+        <f t="shared" si="5"/>
         <v>2.4001964999283868E-2</v>
       </c>
-      <c r="M3" s="49">
+      <c r="M3" s="43">
         <v>1573.973</v>
       </c>
-      <c r="N3" s="49">
+      <c r="N3" s="43">
         <v>1600.0219999999999</v>
       </c>
-      <c r="O3" s="49">
+      <c r="O3" s="43">
         <v>1478.94</v>
       </c>
-      <c r="P3" s="49">
+      <c r="P3" s="43">
         <v>1640.7539999999999</v>
       </c>
-      <c r="Q3" s="51">
+      <c r="Q3" s="45">
         <f>M3/Fig2Fig3Context!F$41</f>
         <v>3.5907646121894274E-2</v>
       </c>
-      <c r="R3" s="51">
+      <c r="R3" s="45">
         <f>N3/Fig2Fig3Context!G$41</f>
         <v>3.840138565394341E-2</v>
       </c>
-      <c r="S3" s="51">
+      <c r="S3" s="45">
         <f>O3/Fig2Fig3Context!H$41</f>
         <v>2.4001964999283868E-2</v>
       </c>
-      <c r="T3" s="51">
+      <c r="T3" s="45">
         <f>P3/Fig2Fig3Context!I$41</f>
         <v>4.7688412914445956E-2</v>
       </c>
-      <c r="U3" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V3" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W3" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="U3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="3">
         <v>0</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="42">
         <f>D4/Fig2Fig3Context!$F$6</f>
         <v>0</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="49">
-        <f>AVERAGE(M4:P4)</f>
+      <c r="G4" s="43">
+        <f t="shared" si="0"/>
         <v>2867.1449009118028</v>
       </c>
-      <c r="H4" s="49">
-        <f>MAX(M4:P4)</f>
+      <c r="H4" s="43">
+        <f t="shared" si="1"/>
         <v>2892.9206476445202</v>
       </c>
-      <c r="I4" s="49">
-        <f>MIN(M4:P4)</f>
+      <c r="I4" s="43">
+        <f t="shared" si="2"/>
         <v>2858.5529847508401</v>
       </c>
-      <c r="J4" s="50">
-        <f>AVERAGE(Q4:T4)</f>
+      <c r="J4" s="44">
+        <f t="shared" si="3"/>
         <v>6.5963355351944933E-2</v>
       </c>
-      <c r="K4" s="50">
-        <f>MAX(Q4:T4)</f>
+      <c r="K4" s="44">
+        <f t="shared" si="4"/>
         <v>8.308366462895718E-2</v>
       </c>
-      <c r="L4" s="50">
-        <f>MIN(Q4:T4)</f>
+      <c r="L4" s="44">
+        <f t="shared" si="5"/>
         <v>4.694969378775974E-2</v>
       </c>
-      <c r="M4" s="49">
+      <c r="M4" s="43">
         <v>2858.5529858323098</v>
       </c>
-      <c r="N4" s="49">
+      <c r="N4" s="43">
         <v>2858.5529854195402</v>
       </c>
-      <c r="O4" s="49">
+      <c r="O4" s="43">
         <v>2892.9206476445202</v>
       </c>
-      <c r="P4" s="49">
+      <c r="P4" s="43">
         <v>2858.5529847508401</v>
       </c>
-      <c r="Q4" s="51">
+      <c r="Q4" s="45">
         <f>M4/Fig2Fig3Context!F$41</f>
         <v>6.5213259081287181E-2</v>
       </c>
-      <c r="R4" s="51">
+      <c r="R4" s="45">
         <f>N4/Fig2Fig3Context!G$41</f>
         <v>6.8606803909775638E-2</v>
       </c>
-      <c r="S4" s="51">
+      <c r="S4" s="45">
         <f>O4/Fig2Fig3Context!H$41</f>
         <v>4.694969378775974E-2</v>
       </c>
-      <c r="T4" s="51">
+      <c r="T4" s="45">
         <f>P4/Fig2Fig3Context!I$41</f>
         <v>8.308366462895718E-2</v>
       </c>
-      <c r="U4" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W4" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="U4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" t="s">
         <v>237</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="43">
         <v>2503.88</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="42">
         <f>D5/Fig2Fig3Context!$F$6</f>
         <v>8.0992843887545227E-2</v>
       </c>
-      <c r="F5" s="47">
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="49">
-        <f>AVERAGE(M5:P5)</f>
+      <c r="G5" s="43">
+        <f t="shared" si="0"/>
         <v>2836.0816082951724</v>
       </c>
-      <c r="H5" s="49">
-        <f>MAX(M5:P5)</f>
+      <c r="H5" s="43">
+        <f t="shared" si="1"/>
         <v>3055.9501099324102</v>
       </c>
-      <c r="I5" s="49">
-        <f>MIN(M5:P5)</f>
+      <c r="I5" s="43">
+        <f t="shared" si="2"/>
         <v>2538.6210134628</v>
       </c>
-      <c r="J5" s="50">
-        <f>AVERAGE(Q5:T5)</f>
+      <c r="J5" s="44">
+        <f t="shared" si="3"/>
         <v>6.6163930889303071E-2</v>
       </c>
-      <c r="K5" s="50">
-        <f>MAX(Q5:T5)</f>
+      <c r="K5" s="44">
+        <f t="shared" si="4"/>
         <v>8.8820999789367153E-2</v>
       </c>
-      <c r="L5" s="50">
-        <f>MIN(Q5:T5)</f>
+      <c r="L5" s="44">
+        <f t="shared" si="5"/>
         <v>4.1199705675403105E-2</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="43">
         <v>2832.14238106625</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="43">
         <v>2917.6129287192298</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="43">
         <v>2538.6210134628</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="43">
         <v>3055.9501099324102</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="45">
         <f>M5/Fig2Fig3Context!F$41</f>
         <v>6.4610743885788344E-2</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="45">
         <f>N5/Fig2Fig3Context!G$41</f>
         <v>7.0024274206653692E-2</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="45">
         <f>O5/Fig2Fig3Context!H$41</f>
         <v>4.1199705675403105E-2</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="45">
         <f>P5/Fig2Fig3Context!I$41</f>
         <v>8.8820999789367153E-2</v>
       </c>
-      <c r="U5" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V5" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W5" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="U5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" t="s">
         <v>237</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="43">
         <v>2129.12</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="42">
         <f>D6/Fig2Fig3Context!$F$6</f>
         <v>6.8870506485075283E-2</v>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="49">
-        <f>AVERAGE(M6:P6)</f>
+      <c r="G6" s="43">
+        <f t="shared" si="0"/>
         <v>2836.0816082951724</v>
       </c>
-      <c r="H6" s="49">
-        <f>MAX(M6:P6)</f>
+      <c r="H6" s="43">
+        <f t="shared" si="1"/>
         <v>3055.9501099324102</v>
       </c>
-      <c r="I6" s="49">
-        <f>MIN(M6:P6)</f>
+      <c r="I6" s="43">
+        <f t="shared" si="2"/>
         <v>2538.6210134628</v>
       </c>
-      <c r="J6" s="50">
-        <f>AVERAGE(Q6:T6)</f>
+      <c r="J6" s="44">
+        <f t="shared" si="3"/>
         <v>6.6163930889303071E-2</v>
       </c>
-      <c r="K6" s="50">
-        <f>MAX(Q6:T6)</f>
+      <c r="K6" s="44">
+        <f t="shared" si="4"/>
         <v>8.8820999789367153E-2</v>
       </c>
-      <c r="L6" s="50">
-        <f>MIN(Q6:T6)</f>
+      <c r="L6" s="44">
+        <f t="shared" si="5"/>
         <v>4.1199705675403105E-2</v>
       </c>
-      <c r="M6" s="49">
+      <c r="M6" s="43">
         <v>2832.14238106625</v>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="43">
         <v>2917.6129287192298</v>
       </c>
-      <c r="O6" s="49">
+      <c r="O6" s="43">
         <v>2538.6210134628</v>
       </c>
-      <c r="P6" s="49">
+      <c r="P6" s="43">
         <v>3055.9501099324102</v>
       </c>
-      <c r="Q6" s="51">
+      <c r="Q6" s="45">
         <f>M6/Fig2Fig3Context!F$41</f>
         <v>6.4610743885788344E-2</v>
       </c>
-      <c r="R6" s="51">
+      <c r="R6" s="45">
         <f>N6/Fig2Fig3Context!G$41</f>
         <v>7.0024274206653692E-2</v>
       </c>
-      <c r="S6" s="51">
+      <c r="S6" s="45">
         <f>O6/Fig2Fig3Context!H$41</f>
         <v>4.1199705675403105E-2</v>
       </c>
-      <c r="T6" s="51">
+      <c r="T6" s="45">
         <f>P6/Fig2Fig3Context!I$41</f>
         <v>8.8820999789367153E-2</v>
       </c>
-      <c r="U6" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V6" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W6" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="U6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" t="s">
         <v>242</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="43">
         <v>2777.65</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="42">
         <f>D7/Fig2Fig3Context!$F$6</f>
         <v>8.9848464313082105E-2</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="49">
-        <f>AVERAGE(M7:P7)</f>
+      <c r="G7" s="43">
+        <f t="shared" si="0"/>
         <v>2836.0816082951724</v>
       </c>
-      <c r="H7" s="49">
-        <f>MAX(M7:P7)</f>
+      <c r="H7" s="43">
+        <f t="shared" si="1"/>
         <v>3055.9501099324102</v>
       </c>
-      <c r="I7" s="49">
-        <f>MIN(M7:P7)</f>
+      <c r="I7" s="43">
+        <f t="shared" si="2"/>
         <v>2538.6210134628</v>
       </c>
-      <c r="J7" s="50">
-        <f>AVERAGE(Q7:T7)</f>
+      <c r="J7" s="44">
+        <f t="shared" si="3"/>
         <v>6.6163930889303071E-2</v>
       </c>
-      <c r="K7" s="50">
-        <f>MAX(Q7:T7)</f>
+      <c r="K7" s="44">
+        <f t="shared" si="4"/>
         <v>8.8820999789367153E-2</v>
       </c>
-      <c r="L7" s="50">
-        <f>MIN(Q7:T7)</f>
+      <c r="L7" s="44">
+        <f t="shared" si="5"/>
         <v>4.1199705675403105E-2</v>
       </c>
-      <c r="M7" s="49">
+      <c r="M7" s="43">
         <v>2832.14238106625</v>
       </c>
-      <c r="N7" s="49">
+      <c r="N7" s="43">
         <v>2917.6129287192298</v>
       </c>
-      <c r="O7" s="49">
+      <c r="O7" s="43">
         <v>2538.6210134628</v>
       </c>
-      <c r="P7" s="49">
+      <c r="P7" s="43">
         <v>3055.9501099324102</v>
       </c>
-      <c r="Q7" s="51">
+      <c r="Q7" s="45">
         <f>M7/Fig2Fig3Context!F$41</f>
         <v>6.4610743885788344E-2</v>
       </c>
-      <c r="R7" s="51">
+      <c r="R7" s="45">
         <f>N7/Fig2Fig3Context!G$41</f>
         <v>7.0024274206653692E-2</v>
       </c>
-      <c r="S7" s="51">
+      <c r="S7" s="45">
         <f>O7/Fig2Fig3Context!H$41</f>
         <v>4.1199705675403105E-2</v>
       </c>
-      <c r="T7" s="51">
+      <c r="T7" s="45">
         <f>P7/Fig2Fig3Context!I$41</f>
         <v>8.8820999789367153E-2</v>
       </c>
-      <c r="U7" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V7" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W7" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="U7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>239</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" t="s">
         <v>240</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="43">
         <v>6891.22</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="42">
         <f>D8/Fig2Fig3Context!$F$6</f>
         <v>0.22290984618061946</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="49">
-        <f>AVERAGE(M8:P8)</f>
+      <c r="G8" s="43">
+        <f t="shared" si="0"/>
         <v>4117.161748457147</v>
       </c>
-      <c r="H8" s="49">
-        <f>MAX(M8:P8)</f>
+      <c r="H8" s="43">
+        <f t="shared" si="1"/>
         <v>4153.3085347241804</v>
       </c>
-      <c r="I8" s="49">
-        <f>MIN(M8:P8)</f>
+      <c r="I8" s="43">
+        <f t="shared" si="2"/>
         <v>4105.11281772855</v>
       </c>
-      <c r="J8" s="50">
-        <f>AVERAGE(Q8:T8)</f>
+      <c r="J8" s="44">
+        <f t="shared" si="3"/>
         <v>9.4724000132910283E-2</v>
       </c>
-      <c r="K8" s="50">
-        <f>MAX(Q8:T8)</f>
+      <c r="K8" s="44">
+        <f t="shared" si="4"/>
         <v>0.11931484860754497</v>
       </c>
-      <c r="L8" s="50">
-        <f>MIN(Q8:T8)</f>
+      <c r="L8" s="44">
+        <f t="shared" si="5"/>
         <v>6.7404739936492861E-2</v>
       </c>
-      <c r="M8" s="49">
+      <c r="M8" s="43">
         <v>4105.11281975765</v>
       </c>
-      <c r="N8" s="49">
+      <c r="N8" s="43">
         <v>4105.1128216182096</v>
       </c>
-      <c r="O8" s="49">
+      <c r="O8" s="43">
         <v>4153.3085347241804</v>
       </c>
-      <c r="P8" s="49">
+      <c r="P8" s="43">
         <v>4105.11281772855</v>
       </c>
-      <c r="Q8" s="51">
+      <c r="Q8" s="45">
         <f>M8/Fig2Fig3Context!F$41</f>
         <v>9.3651503820147641E-2</v>
       </c>
-      <c r="R8" s="51">
+      <c r="R8" s="45">
         <f>N8/Fig2Fig3Context!G$41</f>
         <v>9.8524908167455613E-2</v>
       </c>
-      <c r="S8" s="51">
+      <c r="S8" s="45">
         <f>O8/Fig2Fig3Context!H$41</f>
         <v>6.7404739936492861E-2</v>
       </c>
-      <c r="T8" s="51">
+      <c r="T8" s="45">
         <f>P8/Fig2Fig3Context!I$41</f>
         <v>0.11931484860754497</v>
       </c>
-      <c r="U8" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V8" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W8" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="U8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="42">
         <f>D9/Fig2Fig3Context!$F$6</f>
         <v>0</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G9" s="49">
-        <f>AVERAGE(M9:P9)</f>
+      <c r="G9" s="43">
+        <f t="shared" si="0"/>
         <v>7079.9994819587055</v>
       </c>
-      <c r="H9" s="49">
-        <f>MAX(M9:P9)</f>
+      <c r="H9" s="43">
+        <f t="shared" si="1"/>
         <v>7157.53702501927</v>
       </c>
-      <c r="I9" s="49">
-        <f>MIN(M9:P9)</f>
+      <c r="I9" s="43">
+        <f t="shared" si="2"/>
         <v>7054.1536335278097</v>
       </c>
-      <c r="J9" s="50">
-        <f>AVERAGE(Q9:T9)</f>
+      <c r="J9" s="44">
+        <f t="shared" si="3"/>
         <v>0.16285549211444578</v>
       </c>
-      <c r="K9" s="50">
-        <f>MAX(Q9:T9)</f>
+      <c r="K9" s="44">
+        <f t="shared" si="4"/>
         <v>0.20502853644772775</v>
       </c>
-      <c r="L9" s="50">
-        <f>MIN(Q9:T9)</f>
+      <c r="L9" s="44">
+        <f t="shared" si="5"/>
         <v>0.11616086734795929</v>
       </c>
-      <c r="M9" s="49">
+      <c r="M9" s="43">
         <v>7054.1536335278097</v>
       </c>
-      <c r="N9" s="49">
+      <c r="N9" s="43">
         <v>7054.1536346455796</v>
       </c>
-      <c r="O9" s="49">
+      <c r="O9" s="43">
         <v>7157.53702501927</v>
       </c>
-      <c r="P9" s="49">
+      <c r="P9" s="43">
         <v>7054.1536346421599</v>
       </c>
-      <c r="Q9" s="48">
+      <c r="Q9" s="42">
         <f>M9/Fig2Fig3Context!F$41</f>
         <v>0.1609290962184175</v>
       </c>
-      <c r="R9" s="48">
+      <c r="R9" s="42">
         <f>N9/Fig2Fig3Context!G$41</f>
         <v>0.16930346844367861</v>
       </c>
-      <c r="S9" s="48">
+      <c r="S9" s="42">
         <f>O9/Fig2Fig3Context!H$41</f>
         <v>0.11616086734795929</v>
       </c>
-      <c r="T9" s="48">
+      <c r="T9" s="42">
         <f>P9/Fig2Fig3Context!I$41</f>
         <v>0.20502853644772775</v>
       </c>
-      <c r="U9" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V9" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W9" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="U9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" t="s">
         <v>156</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="4">
         <v>8.3505000000000003</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="42">
         <f>D10/Fig2Fig3Context!$F$8</f>
         <v>0.12017535569847414</v>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="3">
         <v>3</v>
       </c>
-      <c r="G10" s="52">
-        <f>AVERAGE(M10:P10)</f>
+      <c r="G10" s="4">
+        <f t="shared" si="0"/>
         <v>18.681767499999999</v>
       </c>
-      <c r="H10" s="52">
-        <f>MAX(M10:P10)</f>
+      <c r="H10" s="4">
+        <f t="shared" si="1"/>
         <v>19.76079</v>
       </c>
-      <c r="I10" s="52">
-        <f>MIN(M10:P10)</f>
+      <c r="I10" s="4">
+        <f t="shared" si="2"/>
         <v>17.429490000000001</v>
       </c>
-      <c r="J10" s="50">
-        <f>AVERAGE(Q10:T10)</f>
+      <c r="J10" s="44">
+        <f t="shared" si="3"/>
         <v>0.16947323418653204</v>
       </c>
-      <c r="K10" s="50">
-        <f>MAX(Q10:T10)</f>
+      <c r="K10" s="44">
+        <f t="shared" si="4"/>
         <v>0.18863244669799292</v>
       </c>
-      <c r="L10" s="50">
-        <f>MIN(Q10:T10)</f>
+      <c r="L10" s="44">
+        <f t="shared" si="5"/>
         <v>0.14140586246618525</v>
       </c>
-      <c r="M10" s="52">
+      <c r="M10" s="4">
         <v>18.892589999999998</v>
       </c>
-      <c r="N10" s="52">
+      <c r="N10" s="4">
         <v>19.76079</v>
       </c>
-      <c r="O10" s="52">
+      <c r="O10" s="4">
         <v>17.429490000000001</v>
       </c>
-      <c r="P10" s="52">
+      <c r="P10" s="4">
         <v>18.644200000000001</v>
       </c>
-      <c r="Q10" s="48">
+      <c r="Q10" s="42">
         <f>M10/Fig2Fig3Context!F$42</f>
         <v>0.1803447876406781</v>
       </c>
-      <c r="R10" s="48">
+      <c r="R10" s="42">
         <f>N10/Fig2Fig3Context!G$42</f>
         <v>0.18863244669799292</v>
       </c>
-      <c r="S10" s="48">
+      <c r="S10" s="42">
         <f>O10/Fig2Fig3Context!H$42</f>
         <v>0.14140586246618525</v>
       </c>
-      <c r="T10" s="48">
+      <c r="T10" s="42">
         <f>P10/Fig2Fig3Context!I$42</f>
         <v>0.16750983994127186</v>
       </c>
-      <c r="U10" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V10" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W10" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="U10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" t="s">
         <v>235</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="4">
         <f>58000000*1.65*14825/1000000000000</f>
         <v>1.4187525000000001</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="42">
         <f>D11/Fig2Fig3Context!$F$8</f>
         <v>2.0417829631231593E-2</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="3">
         <v>10</v>
       </c>
-      <c r="G11" s="52">
-        <f>AVERAGE(M11:P11)</f>
+      <c r="G11" s="4">
+        <f t="shared" si="0"/>
         <v>19.010424999999998</v>
       </c>
-      <c r="H11" s="52">
-        <f>MAX(M11:P11)</f>
+      <c r="H11" s="4">
+        <f t="shared" si="1"/>
         <v>20.128129999999999</v>
       </c>
-      <c r="I11" s="52">
-        <f>MIN(M11:P11)</f>
+      <c r="I11" s="4">
+        <f t="shared" si="2"/>
         <v>17.714639999999999</v>
       </c>
-      <c r="J11" s="50">
-        <f>AVERAGE(Q11:T11)</f>
+      <c r="J11" s="44">
+        <f t="shared" si="3"/>
         <v>0.17246256031456719</v>
       </c>
-      <c r="K11" s="50">
-        <f>MAX(Q11:T11)</f>
+      <c r="K11" s="44">
+        <f t="shared" si="4"/>
         <v>0.1921389989648831</v>
       </c>
-      <c r="L11" s="50">
-        <f>MIN(Q11:T11)</f>
+      <c r="L11" s="44">
+        <f t="shared" si="5"/>
         <v>0.14371929112544221</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11" s="4">
         <v>19.228079999999999</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11" s="4">
         <v>20.128129999999999</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11" s="4">
         <v>17.714639999999999</v>
       </c>
-      <c r="P11" s="52">
+      <c r="P11" s="4">
         <v>18.970849999999999</v>
       </c>
-      <c r="Q11" s="48">
+      <c r="Q11" s="42">
         <f>M11/Fig2Fig3Context!F$42</f>
         <v>0.18354730634274971</v>
       </c>
-      <c r="R11" s="48">
+      <c r="R11" s="42">
         <f>N11/Fig2Fig3Context!G$42</f>
         <v>0.1921389989648831</v>
       </c>
-      <c r="S11" s="48">
+      <c r="S11" s="42">
         <f>O11/Fig2Fig3Context!H$42</f>
         <v>0.14371929112544221</v>
       </c>
-      <c r="T11" s="48">
+      <c r="T11" s="42">
         <f>P11/Fig2Fig3Context!I$42</f>
         <v>0.17044464482519373</v>
       </c>
-      <c r="U11" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V11" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W11" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="U11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" t="s">
         <v>234</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="4">
         <f>0.1057 * 5.86 / 0.664 * 1.65</f>
         <v>1.5391766566265059</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="42">
         <f>D12/Fig2Fig3Context!$F$8</f>
         <v>2.2150901406248553E-2</v>
       </c>
-      <c r="F12" s="47">
-        <v>11</v>
-      </c>
-      <c r="G12" s="52">
-        <f>AVERAGE(M12:P12)</f>
+      <c r="F12" s="3">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="0"/>
         <v>19.994799999999998</v>
       </c>
-      <c r="H12" s="52">
-        <f>MAX(M12:P12)</f>
+      <c r="H12" s="4">
+        <f t="shared" si="1"/>
         <v>21.152259999999998</v>
       </c>
-      <c r="I12" s="52">
-        <f>MIN(M12:P12)</f>
+      <c r="I12" s="4">
+        <f t="shared" si="2"/>
         <v>18.65372</v>
       </c>
-      <c r="J12" s="50">
-        <f>AVERAGE(Q12:T12)</f>
+      <c r="J12" s="44">
+        <f t="shared" si="3"/>
         <v>0.18138469942480542</v>
       </c>
-      <c r="K12" s="50">
-        <f>MAX(Q12:T12)</f>
+      <c r="K12" s="44">
+        <f t="shared" si="4"/>
         <v>0.20191513380750908</v>
       </c>
-      <c r="L12" s="50">
-        <f>MIN(Q12:T12)</f>
+      <c r="L12" s="44">
+        <f t="shared" si="5"/>
         <v>0.15133806926093241</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12" s="4">
         <v>20.2179</v>
       </c>
-      <c r="N12" s="52">
+      <c r="N12" s="4">
         <v>21.152259999999998</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12" s="4">
         <v>18.65372</v>
       </c>
-      <c r="P12" s="52">
+      <c r="P12" s="4">
         <v>19.95532</v>
       </c>
-      <c r="Q12" s="48">
+      <c r="Q12" s="42">
         <f>M12/Fig2Fig3Context!F$42</f>
         <v>0.19299592496531529</v>
       </c>
-      <c r="R12" s="48">
+      <c r="R12" s="42">
         <f>N12/Fig2Fig3Context!G$42</f>
         <v>0.20191513380750908</v>
       </c>
-      <c r="S12" s="48">
+      <c r="S12" s="42">
         <f>O12/Fig2Fig3Context!H$42</f>
         <v>0.15133806926093241</v>
       </c>
-      <c r="T12" s="48">
+      <c r="T12" s="42">
         <f>P12/Fig2Fig3Context!I$42</f>
         <v>0.17928966966546492</v>
       </c>
-      <c r="U12" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V12" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W12" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="U12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" t="s">
         <v>233</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" t="s">
         <v>156</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="4">
         <v>22.3948384729262</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="42">
         <f>D13/Fig2Fig3Context!$F$8</f>
         <v>0.32229299793949817</v>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="3">
         <v>3</v>
       </c>
-      <c r="G13" s="52">
-        <f>AVERAGE(M13:P13)</f>
+      <c r="G13" s="4">
+        <f t="shared" si="0"/>
         <v>21.327185</v>
       </c>
-      <c r="H13" s="52">
-        <f>MAX(M13:P13)</f>
+      <c r="H13" s="4">
+        <f t="shared" si="1"/>
         <v>22.737269999999999</v>
       </c>
-      <c r="I13" s="52">
-        <f>MIN(M13:P13)</f>
+      <c r="I13" s="4">
+        <f t="shared" si="2"/>
         <v>19.704660000000001</v>
       </c>
-      <c r="J13" s="50">
-        <f>AVERAGE(Q13:T13)</f>
+      <c r="J13" s="44">
+        <f t="shared" si="3"/>
         <v>0.19354226934140906</v>
       </c>
-      <c r="K13" s="50">
-        <f>MAX(Q13:T13)</f>
+      <c r="K13" s="44">
+        <f t="shared" si="4"/>
         <v>0.21704531404528227</v>
       </c>
-      <c r="L13" s="50">
-        <f>MIN(Q13:T13)</f>
+      <c r="L13" s="44">
+        <f t="shared" si="5"/>
         <v>0.15986437020836189</v>
       </c>
-      <c r="M13" s="52">
+      <c r="M13" s="4">
         <v>21.595369999999999</v>
       </c>
-      <c r="N13" s="52">
+      <c r="N13" s="4">
         <v>22.737269999999999</v>
       </c>
-      <c r="O13" s="52">
+      <c r="O13" s="4">
         <v>19.704660000000001</v>
       </c>
-      <c r="P13" s="52">
+      <c r="P13" s="4">
         <v>21.271439999999998</v>
       </c>
-      <c r="Q13" s="48">
+      <c r="Q13" s="42">
         <f>M13/Fig2Fig3Context!F$42</f>
         <v>0.20614497094743869</v>
       </c>
-      <c r="R13" s="48">
+      <c r="R13" s="42">
         <f>N13/Fig2Fig3Context!G$42</f>
         <v>0.21704531404528227</v>
       </c>
-      <c r="S13" s="48">
+      <c r="S13" s="42">
         <f>O13/Fig2Fig3Context!H$42</f>
         <v>0.15986437020836189</v>
       </c>
-      <c r="T13" s="48">
+      <c r="T13" s="42">
         <f>P13/Fig2Fig3Context!I$42</f>
         <v>0.19111442216455343</v>
       </c>
-      <c r="U13" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V13" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W13" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="17" t="s">
+      <c r="U13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" t="s">
         <v>232</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" t="s">
         <v>290</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="4">
         <v>4.1939755324574808</v>
       </c>
-      <c r="E14" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="47">
+      <c r="E14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="3">
         <v>3</v>
       </c>
-      <c r="G14" s="52">
-        <f>AVERAGE(M14:P14)</f>
+      <c r="G14" s="4">
+        <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="H14" s="52">
-        <f>MAX(M14:P14)</f>
+      <c r="H14" s="4">
+        <f t="shared" si="1"/>
         <v>-2</v>
       </c>
-      <c r="I14" s="52">
-        <f>MIN(M14:P14)</f>
+      <c r="I14" s="4">
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
-      <c r="J14" s="50">
-        <f>AVERAGE(Q14:T14)</f>
+      <c r="J14" s="44">
+        <f t="shared" si="3"/>
         <v>-0.36152696552073943</v>
       </c>
-      <c r="K14" s="50">
-        <f>MAX(Q14:T14)</f>
+      <c r="K14" s="44">
+        <f t="shared" si="4"/>
         <v>-0.28544254441200551</v>
       </c>
-      <c r="L14" s="50">
-        <f>MIN(Q14:T14)</f>
+      <c r="L14" s="44">
+        <f t="shared" si="5"/>
         <v>-0.434785727810656</v>
       </c>
-      <c r="M14" s="52">
+      <c r="M14" s="4">
         <v>-2</v>
       </c>
-      <c r="N14" s="52">
+      <c r="N14" s="4">
         <v>-2</v>
       </c>
-      <c r="O14" s="52">
+      <c r="O14" s="4">
         <v>-2</v>
       </c>
-      <c r="P14" s="52">
+      <c r="P14" s="4">
         <v>-2</v>
       </c>
-      <c r="Q14" s="48">
+      <c r="Q14" s="42">
         <f>M14/Fig2Fig3Context!F$48</f>
         <v>-0.38104332329220669</v>
       </c>
-      <c r="R14" s="48">
+      <c r="R14" s="42">
         <f>N14/Fig2Fig3Context!G$48</f>
         <v>-0.434785727810656</v>
       </c>
-      <c r="S14" s="48">
+      <c r="S14" s="42">
         <f>O14/Fig2Fig3Context!H$48</f>
         <v>-0.28544254441200551</v>
       </c>
-      <c r="T14" s="48">
+      <c r="T14" s="42">
         <f>P14/Fig2Fig3Context!I$48</f>
         <v>-0.34483626656808947</v>
       </c>
-      <c r="U14" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V14" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W14" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="U14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" t="s">
         <v>231</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="4">
         <v>7.0380769863212302</v>
       </c>
-      <c r="E15" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="47">
+      <c r="E15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="3">
         <v>3</v>
       </c>
-      <c r="G15" s="52">
-        <f>AVERAGE(M15:P15)</f>
+      <c r="G15" s="4">
+        <f t="shared" si="0"/>
         <v>-10.529271250000001</v>
       </c>
-      <c r="H15" s="52">
-        <f>MAX(M15:P15)</f>
+      <c r="H15" s="4">
+        <f t="shared" si="1"/>
         <v>-9.6332950000000004</v>
       </c>
-      <c r="I15" s="52">
-        <f>MIN(M15:P15)</f>
+      <c r="I15" s="4">
+        <f t="shared" si="2"/>
         <v>-11.285500000000001</v>
       </c>
-      <c r="J15" s="50">
-        <f>AVERAGE(Q15:T15)</f>
+      <c r="J15" s="44">
+        <f t="shared" si="3"/>
         <v>-0.70303820595718192</v>
       </c>
-      <c r="K15" s="50">
-        <f>MAX(Q15:T15)</f>
+      <c r="K15" s="44">
+        <f t="shared" si="4"/>
         <v>-0.37194189189189192</v>
       </c>
-      <c r="L15" s="50">
-        <f>MIN(Q15:T15)</f>
+      <c r="L15" s="44">
+        <f t="shared" si="5"/>
         <v>-0.97121342512908793</v>
       </c>
-      <c r="M15" s="52">
+      <c r="M15" s="4">
         <v>-10.773999999999999</v>
       </c>
-      <c r="N15" s="52">
+      <c r="N15" s="4">
         <v>-11.285500000000001</v>
       </c>
-      <c r="O15" s="52">
+      <c r="O15" s="4">
         <v>-9.6332950000000004</v>
       </c>
-      <c r="P15" s="52">
+      <c r="P15" s="4">
         <v>-10.424289999999999</v>
       </c>
-      <c r="Q15" s="48">
+      <c r="Q15" s="42">
         <f>M15/Fig2Fig3Context!F$43</f>
         <v>-0.92719449225473316</v>
       </c>
-      <c r="R15" s="48">
+      <c r="R15" s="42">
         <f>N15/Fig2Fig3Context!G$43</f>
         <v>-0.97121342512908793</v>
       </c>
-      <c r="S15" s="48">
+      <c r="S15" s="42">
         <f>O15/Fig2Fig3Context!H$43</f>
         <v>-0.37194189189189192</v>
       </c>
-      <c r="T15" s="48">
+      <c r="T15" s="42">
         <f>P15/Fig2Fig3Context!I$43</f>
         <v>-0.54180301455301461</v>
       </c>
-      <c r="U15" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V15" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W15" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="U15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" t="s">
         <v>229</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="46">
         <f>0.664/8.9*100</f>
         <v>7.4606741573033712</v>
       </c>
-      <c r="E16" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="47">
+      <c r="E16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="3">
         <v>3</v>
       </c>
-      <c r="G16" s="54">
-        <f>AVERAGE(M16:P16)</f>
+      <c r="G16" s="5">
+        <f t="shared" si="0"/>
         <v>3.7223589999999995</v>
       </c>
-      <c r="H16" s="54">
-        <f>MAX(M16:P16)</f>
+      <c r="H16" s="5">
+        <f t="shared" si="1"/>
         <v>4.456696</v>
       </c>
-      <c r="I16" s="54">
-        <f>MIN(M16:P16)</f>
+      <c r="I16" s="5">
+        <f t="shared" si="2"/>
         <v>3.1308310000000001</v>
       </c>
-      <c r="J16" s="50">
-        <f>AVERAGE(Q16:T16)</f>
+      <c r="J16" s="44">
+        <f t="shared" si="3"/>
         <v>-0.50106935090361449</v>
       </c>
-      <c r="K16" s="50">
-        <f>MAX(Q16:T16)</f>
+      <c r="K16" s="44">
+        <f t="shared" si="4"/>
         <v>-0.40264165060240964</v>
       </c>
-      <c r="L16" s="50">
-        <f>MIN(Q16:T16)</f>
+      <c r="L16" s="44">
+        <f t="shared" si="5"/>
         <v>-0.580355483433735</v>
       </c>
-      <c r="M16" s="54">
+      <c r="M16" s="5">
         <v>3.4088669999999999</v>
       </c>
-      <c r="N16" s="54">
+      <c r="N16" s="5">
         <v>3.1308310000000001</v>
       </c>
-      <c r="O16" s="54">
+      <c r="O16" s="5">
         <v>4.456696</v>
       </c>
-      <c r="P16" s="54">
+      <c r="P16" s="5">
         <v>3.8930419999999999</v>
       </c>
-      <c r="Q16" s="48">
+      <c r="Q16" s="42">
         <f>(M16/$D16)-1</f>
         <v>-0.54308860993975916</v>
       </c>
-      <c r="R16" s="48">
+      <c r="R16" s="42">
         <f>(N16/$D16)-1</f>
         <v>-0.580355483433735</v>
       </c>
-      <c r="S16" s="48">
+      <c r="S16" s="42">
         <f>(O16/$D16)-1</f>
         <v>-0.40264165060240964</v>
       </c>
-      <c r="T16" s="48">
+      <c r="T16" s="42">
         <f>(P16/$D16)-1</f>
         <v>-0.47819165963855426</v>
       </c>
-      <c r="U16" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V16" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W16" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="U16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" t="s">
         <v>228</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" t="s">
         <v>291</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="4">
         <v>1.508</v>
       </c>
-      <c r="E17" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="47">
+      <c r="E17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="3">
         <v>3</v>
       </c>
-      <c r="G17" s="54">
-        <f>AVERAGE(M17:P17)</f>
+      <c r="G17" s="5">
+        <f t="shared" si="0"/>
         <v>0.75069753333333333</v>
       </c>
-      <c r="H17" s="54">
-        <f>MAX(M17:P17)</f>
+      <c r="H17" s="5">
+        <f t="shared" si="1"/>
         <v>0.89050090000000004</v>
       </c>
-      <c r="I17" s="54">
-        <f>MIN(M17:P17)</f>
+      <c r="I17" s="5">
+        <f t="shared" si="2"/>
         <v>0.58800989999999997</v>
       </c>
-      <c r="J17" s="50">
-        <f>AVERAGE(Q17:T17)</f>
+      <c r="J17" s="44">
+        <f t="shared" si="3"/>
         <v>-0.50218996463306809</v>
       </c>
-      <c r="K17" s="50">
-        <f>MAX(Q17:T17)</f>
+      <c r="K17" s="44">
+        <f t="shared" si="4"/>
         <v>-0.40948216180371355</v>
       </c>
-      <c r="L17" s="50">
-        <f>MIN(Q17:T17)</f>
+      <c r="L17" s="44">
+        <f t="shared" si="5"/>
         <v>-0.61007301061007957</v>
       </c>
-      <c r="M17" s="54">
+      <c r="M17" s="5">
         <v>0.77358179999999999</v>
       </c>
-      <c r="N17" s="54">
+      <c r="N17" s="5">
         <v>0.58800989999999997</v>
       </c>
-      <c r="O17" s="54">
+      <c r="O17" s="5">
         <v>0.89050090000000004</v>
       </c>
-      <c r="P17" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q17" s="48">
+      <c r="P17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q17" s="42">
         <f>(M17/$D17)-1</f>
         <v>-0.48701472148541114</v>
       </c>
-      <c r="R17" s="48">
+      <c r="R17" s="42">
         <f>(N17/$D17)-1</f>
         <v>-0.61007301061007957</v>
       </c>
-      <c r="S17" s="48">
+      <c r="S17" s="42">
         <f>(O17/$D17)-1</f>
         <v>-0.40948216180371355</v>
       </c>
-      <c r="T17" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U17" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V17" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W17" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="T17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" t="s">
         <v>226</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="43">
         <v>1601.7224701276987</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="42">
         <f>D18/Fig2Fig3Context!F9</f>
         <v>0.14494928015502909</v>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="49">
-        <f>AVERAGE(M18:P18)</f>
+      <c r="G18" s="43">
+        <f t="shared" si="0"/>
         <v>5048.4187500000007</v>
       </c>
-      <c r="H18" s="49">
-        <f>MAX(M18:P18)</f>
+      <c r="H18" s="43">
+        <f t="shared" si="1"/>
         <v>6001.991</v>
       </c>
-      <c r="I18" s="49">
-        <f>MIN(M18:P18)</f>
+      <c r="I18" s="43">
+        <f t="shared" si="2"/>
         <v>4478.1440000000002</v>
       </c>
-      <c r="J18" s="50">
-        <f>AVERAGE(Q18:T18)</f>
+      <c r="J18" s="44">
+        <f t="shared" si="3"/>
         <v>0.38028240094393784</v>
       </c>
-      <c r="K18" s="50">
-        <f>MAX(Q18:T18)</f>
+      <c r="K18" s="44">
+        <f t="shared" si="4"/>
         <v>0.61266378134843846</v>
       </c>
-      <c r="L18" s="50">
-        <f>MIN(Q18:T18)</f>
+      <c r="L18" s="44">
+        <f t="shared" si="5"/>
         <v>0.25584506531181</v>
       </c>
-      <c r="M18" s="49">
+      <c r="M18" s="43">
         <v>4590.7250000000004</v>
       </c>
-      <c r="N18" s="49">
+      <c r="N18" s="43">
         <v>5122.8149999999996</v>
       </c>
-      <c r="O18" s="49">
+      <c r="O18" s="43">
         <v>4478.1440000000002</v>
       </c>
-      <c r="P18" s="49">
+      <c r="P18" s="43">
         <v>6001.991</v>
       </c>
-      <c r="Q18" s="48">
+      <c r="Q18" s="42">
         <f>M18/Fig2Fig3Context!F$44</f>
         <v>0.30392325931699959</v>
       </c>
-      <c r="R18" s="48">
+      <c r="R18" s="42">
         <f>N18/Fig2Fig3Context!G$44</f>
         <v>0.34869749779850345</v>
       </c>
-      <c r="S18" s="48">
+      <c r="S18" s="42">
         <f>O18/Fig2Fig3Context!H$44</f>
         <v>0.25584506531181</v>
       </c>
-      <c r="T18" s="48">
+      <c r="T18" s="42">
         <f>P18/Fig2Fig3Context!I$44</f>
         <v>0.61266378134843846</v>
       </c>
-      <c r="U18" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V18" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W18" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="U18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" t="s">
         <v>225</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" t="s">
         <v>224</v>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="43">
         <v>348.57777394599998</v>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="42">
         <f>D19/Fig2Fig3Context!F10</f>
         <v>0.38433760090264452</v>
       </c>
-      <c r="F19" s="47">
+      <c r="F19" s="3">
         <v>4</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="43">
         <f>U19</f>
         <v>660.19099700000004</v>
       </c>
-      <c r="H19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J19" s="51">
+      <c r="H19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="45">
         <f>U19/Fig2Fig3Context!F10</f>
         <v>0.72791853895943637</v>
       </c>
-      <c r="K19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U19" s="49">
+      <c r="K19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U19" s="43">
         <v>660.19099700000004</v>
       </c>
-      <c r="V19" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W19" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="V19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" t="s">
         <v>223</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" t="s">
         <v>222</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="42">
         <f>D20/Fig2Fig3Context!$F$6</f>
         <v>0</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="43">
         <f>AVERAGE(M20:P20)</f>
         <v>1541.0630000000001</v>
       </c>
-      <c r="H20" s="49">
+      <c r="H20" s="43">
         <f>MAX(M20:P20)</f>
         <v>1541.0630000000001</v>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="43">
         <f>MIN(M20:P20)</f>
         <v>1541.0630000000001</v>
       </c>
-      <c r="J20" s="50">
+      <c r="J20" s="44">
         <f>AVERAGE(Q20:T20)</f>
         <v>3.5486066392675736E-2</v>
       </c>
-      <c r="K20" s="50">
+      <c r="K20" s="44">
         <f>MAX(Q20:T20)</f>
         <v>4.4790900202696347E-2</v>
       </c>
-      <c r="L20" s="50">
+      <c r="L20" s="44">
         <f>MIN(Q20:T20)</f>
         <v>2.5010169572593478E-2</v>
       </c>
-      <c r="M20" s="49">
+      <c r="M20" s="43">
         <v>1541.0630000000001</v>
       </c>
-      <c r="N20" s="49">
+      <c r="N20" s="43">
         <v>1541.0630000000001</v>
       </c>
-      <c r="O20" s="49">
+      <c r="O20" s="43">
         <v>1541.0630000000001</v>
       </c>
-      <c r="P20" s="49">
+      <c r="P20" s="43">
         <v>1541.0630000000001</v>
       </c>
-      <c r="Q20" s="51">
+      <c r="Q20" s="45">
         <f>M20/Fig2Fig3Context!F$41</f>
         <v>3.5156857745046934E-2</v>
       </c>
-      <c r="R20" s="51">
+      <c r="R20" s="45">
         <f>N20/Fig2Fig3Context!G$41</f>
         <v>3.6986338050366184E-2</v>
       </c>
-      <c r="S20" s="51">
+      <c r="S20" s="45">
         <f>O20/Fig2Fig3Context!H$41</f>
         <v>2.5010169572593478E-2</v>
       </c>
-      <c r="T20" s="51">
+      <c r="T20" s="45">
         <f>P20/Fig2Fig3Context!I$41</f>
         <v>4.4790900202696347E-2</v>
       </c>
-      <c r="U20" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V20" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W20" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="U20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" t="s">
         <v>221</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="3">
         <v>0.6</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="42">
         <f>D21/Fig2Fig3Context!F7</f>
         <v>6.1855670103092781E-3</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="3">
         <v>2</v>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="43">
         <f>AVERAGE(M21:P21)</f>
         <v>152.44113013173433</v>
       </c>
-      <c r="H21" s="49">
+      <c r="H21" s="43">
         <f>MAX(M21:P21)</f>
         <v>155.32303105962066</v>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="43">
         <f>MIN(M21:P21)</f>
         <v>150.3765801544499</v>
       </c>
-      <c r="J21" s="55">
+      <c r="J21" s="47">
         <f>AVERAGE(Q22:T23)</f>
         <v>0.50813710043911442</v>
       </c>
-      <c r="K21" s="55">
+      <c r="K21" s="47">
         <f>MAX(Q22:T23)</f>
         <v>0.77661515529810332</v>
       </c>
-      <c r="L21" s="55">
+      <c r="L21" s="47">
         <f>MIN(Q22:T23)</f>
         <v>0.25062763359074985</v>
       </c>
-      <c r="M21" s="49">
+      <c r="M21" s="43">
         <v>151.67689631943318</v>
       </c>
-      <c r="N21" s="49">
+      <c r="N21" s="43">
         <v>155.32303105962066</v>
       </c>
-      <c r="O21" s="49">
+      <c r="O21" s="43">
         <v>150.3765801544499</v>
       </c>
-      <c r="P21" s="49">
+      <c r="P21" s="43">
         <v>152.38801299343356</v>
       </c>
-      <c r="Q21" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R21" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S21" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T21" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U21" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V21" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W21" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="Q21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" t="s">
         <v>169</v>
       </c>
-      <c r="D22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="K22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q22" s="48">
+      <c r="D22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q22" s="42">
         <f>M21/Fig2Fig3Context!$F34</f>
         <v>0.75838448159716587</v>
       </c>
-      <c r="R22" s="48">
+      <c r="R22" s="42">
         <f>N21/Fig2Fig3Context!$F34</f>
         <v>0.77661515529810332</v>
       </c>
-      <c r="S22" s="48">
+      <c r="S22" s="42">
         <f>O21/Fig2Fig3Context!$F34</f>
         <v>0.75188290077224951</v>
       </c>
-      <c r="T22" s="48">
+      <c r="T22" s="42">
         <f>P21/Fig2Fig3Context!$F34</f>
         <v>0.76194006496716782</v>
       </c>
-      <c r="U22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W22" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="U22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="K23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q23" s="48">
+      <c r="D23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q23" s="42">
         <f>M21/Fig2Fig3Context!$F35</f>
         <v>0.25279482719905533</v>
       </c>
-      <c r="R23" s="48">
+      <c r="R23" s="42">
         <f>N21/Fig2Fig3Context!$F35</f>
         <v>0.25887171843270113</v>
       </c>
-      <c r="S23" s="48">
+      <c r="S23" s="42">
         <f>O21/Fig2Fig3Context!$F35</f>
         <v>0.25062763359074985</v>
       </c>
-      <c r="T23" s="48">
+      <c r="T23" s="42">
         <f>P21/Fig2Fig3Context!$F35</f>
         <v>0.25398002165572259</v>
       </c>
-      <c r="U23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W23" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X23" s="57"/>
-    </row>
-    <row r="24" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="U23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X23" s="49"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" t="s">
         <v>214</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="42">
         <f>D24/Fig2Fig3Context!$F$11</f>
         <v>0</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="5">
         <f>AVERAGE(M24:P24)</f>
         <v>1.2916301239219568</v>
       </c>
-      <c r="H24" s="54">
+      <c r="H24" s="5">
         <f>MAX(M24:P24)</f>
         <v>1.3525722722931439</v>
       </c>
-      <c r="I24" s="54">
+      <c r="I24" s="5">
         <f>MIN(M24:P24)</f>
         <v>1.2147387771808575</v>
       </c>
-      <c r="J24" s="55">
+      <c r="J24" s="47">
         <f>AVERAGE(Q24:T24)</f>
         <v>0.39400737480849074</v>
       </c>
-      <c r="K24" s="55">
+      <c r="K24" s="47">
         <f>MAX(Q24:T24)</f>
         <v>0.44650019019521786</v>
       </c>
-      <c r="L24" s="55">
+      <c r="L24" s="47">
         <f>MIN(Q24:T24)</f>
         <v>0.28312224457709695</v>
       </c>
-      <c r="M24" s="54">
+      <c r="M24" s="5">
         <f>AVERAGE(M25:M26)</f>
         <v>1.3088192073554605</v>
       </c>
-      <c r="N24" s="54">
+      <c r="N24" s="5">
         <f>AVERAGE(N25:N26)</f>
         <v>1.3525722722931439</v>
       </c>
-      <c r="O24" s="54">
+      <c r="O24" s="5">
         <f>AVERAGE(O25:O26)</f>
         <v>1.2147387771808575</v>
       </c>
-      <c r="P24" s="54">
+      <c r="P24" s="5">
         <f>AVERAGE(P25:P26)</f>
         <v>1.2903902388583655</v>
       </c>
-      <c r="Q24" s="48">
+      <c r="Q24" s="42">
         <f>M24/Fig2Fig3Context!F$45</f>
         <v>0.41185684604754424</v>
       </c>
-      <c r="R24" s="48">
+      <c r="R24" s="42">
         <f>N24/Fig2Fig3Context!G$45</f>
         <v>0.43455021841410385</v>
       </c>
-      <c r="S24" s="48">
+      <c r="S24" s="42">
         <f>O24/Fig2Fig3Context!H$45</f>
         <v>0.28312224457709695</v>
       </c>
-      <c r="T24" s="48">
+      <c r="T24" s="42">
         <f>P24/Fig2Fig3Context!I$45</f>
         <v>0.44650019019521786</v>
       </c>
-      <c r="U24" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V24" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W24" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X24" s="57"/>
-    </row>
-    <row r="25" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="U24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X24" s="49"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="48" t="s">
         <v>217</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" t="s">
         <v>214</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="3">
         <v>0</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="42">
         <f>D25/Fig2Fig3Context!$F$11</f>
         <v>0</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="K25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M25" s="54">
+      <c r="G25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25" s="5">
         <v>1.1571800421880618</v>
       </c>
-      <c r="N25" s="54">
+      <c r="N25" s="5">
         <v>1.2302430733978427</v>
       </c>
-      <c r="O25" s="54">
+      <c r="O25" s="5">
         <v>1.0610698120277045</v>
       </c>
-      <c r="P25" s="54">
+      <c r="P25" s="5">
         <v>1.1470523746444159</v>
       </c>
-      <c r="Q25" s="48">
+      <c r="Q25" s="42">
         <f>M25/Fig2Fig3Context!F$45</f>
         <v>0.36413930954430301</v>
       </c>
-      <c r="R25" s="48">
+      <c r="R25" s="42">
         <f>N25/Fig2Fig3Context!G$45</f>
         <v>0.39524867336006292</v>
       </c>
-      <c r="S25" s="48">
+      <c r="S25" s="42">
         <f>O25/Fig2Fig3Context!H$45</f>
         <v>0.24730622951831135</v>
       </c>
-      <c r="T25" s="48">
+      <c r="T25" s="42">
         <f>P25/Fig2Fig3Context!I$45</f>
         <v>0.39690249354003609</v>
       </c>
-      <c r="U25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W25" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X25" s="57"/>
-    </row>
-    <row r="26" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="U25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X25" s="49"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="48" t="s">
         <v>216</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" t="s">
         <v>214</v>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="3">
         <v>0</v>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="42">
         <f>D26/Fig2Fig3Context!$F$11</f>
         <v>0</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="K26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M26" s="54">
+      <c r="G26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M26" s="5">
         <v>1.460458372522859</v>
       </c>
-      <c r="N26" s="54">
+      <c r="N26" s="5">
         <v>1.4749014711884449</v>
       </c>
-      <c r="O26" s="54">
+      <c r="O26" s="5">
         <v>1.3684077423340106</v>
       </c>
-      <c r="P26" s="54">
+      <c r="P26" s="5">
         <v>1.433728103072315</v>
       </c>
-      <c r="Q26" s="48">
+      <c r="Q26" s="42">
         <f>M26/Fig2Fig3Context!F$45</f>
         <v>0.45957438255078542</v>
       </c>
-      <c r="R26" s="48">
+      <c r="R26" s="42">
         <f>N26/Fig2Fig3Context!G$45</f>
         <v>0.47385176346814473</v>
       </c>
-      <c r="S26" s="48">
+      <c r="S26" s="42">
         <f>O26/Fig2Fig3Context!H$45</f>
         <v>0.31893825963588257</v>
       </c>
-      <c r="T26" s="48">
+      <c r="T26" s="42">
         <f>P26/Fig2Fig3Context!I$45</f>
         <v>0.49609788685039968</v>
       </c>
-      <c r="U26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X26" s="57"/>
-    </row>
-    <row r="27" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="U26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X26" s="49"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" t="s">
         <v>215</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" t="s">
         <v>214</v>
       </c>
-      <c r="D27" s="47">
+      <c r="D27" s="3">
         <v>0</v>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="42">
         <f>D27/Fig2Fig3Context!$F$12</f>
         <v>0</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G27" s="54">
+      <c r="G27" s="5">
         <f>AVERAGE(M27:P27)</f>
         <v>4.9535940253807524</v>
       </c>
-      <c r="H27" s="54">
+      <c r="H27" s="5">
         <f>MAX(M27:P27)</f>
         <v>5.0371030842630642</v>
       </c>
-      <c r="I27" s="54">
+      <c r="I27" s="5">
         <f>MIN(M27:P27)</f>
         <v>4.8648678002777705</v>
       </c>
-      <c r="J27" s="55">
+      <c r="J27" s="47">
         <f>AVERAGE(Q27:T27)</f>
         <v>0.92926592370833605</v>
       </c>
-      <c r="K27" s="55">
+      <c r="K27" s="47">
         <f>MAX(Q27:T27)</f>
         <v>1.0586838344789153</v>
       </c>
-      <c r="L27" s="55">
+      <c r="L27" s="47">
         <f>MIN(Q27:T27)</f>
         <v>0.63696144490078421</v>
       </c>
-      <c r="M27" s="54">
+      <c r="M27" s="5">
         <v>4.9316927635249437</v>
       </c>
-      <c r="N27" s="54">
+      <c r="N27" s="5">
         <v>4.8648678002777705</v>
       </c>
-      <c r="O27" s="54">
+      <c r="O27" s="5">
         <v>4.9807124534572313</v>
       </c>
-      <c r="P27" s="54">
+      <c r="P27" s="5">
         <v>5.0371030842630642</v>
       </c>
-      <c r="Q27" s="48">
+      <c r="Q27" s="42">
         <f>M27/Fig2Fig3Context!F46</f>
         <v>1.040231525673786</v>
       </c>
-      <c r="R27" s="48">
+      <c r="R27" s="42">
         <f>N27/Fig2Fig3Context!G46</f>
         <v>1.0586838344789153</v>
       </c>
-      <c r="S27" s="48">
+      <c r="S27" s="42">
         <f>O27/Fig2Fig3Context!H46</f>
         <v>0.63696144490078421</v>
       </c>
-      <c r="T27" s="48">
+      <c r="T27" s="42">
         <f>P27/Fig2Fig3Context!I46</f>
         <v>0.98118688977985902</v>
       </c>
-      <c r="U27" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V27" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W27" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A28" s="17" t="s">
+      <c r="U27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" t="s">
         <v>213</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" t="s">
         <v>292</v>
       </c>
-      <c r="D28" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="49">
+      <c r="D28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="43">
         <f>AVERAGE(M28:P28)</f>
         <v>-30</v>
       </c>
-      <c r="H28" s="49">
+      <c r="H28" s="43">
         <f>MAX(M28:P28)</f>
         <v>-30</v>
       </c>
-      <c r="I28" s="49">
+      <c r="I28" s="43">
         <f>MIN(M28:P28)</f>
         <v>-30</v>
       </c>
-      <c r="J28" s="55">
+      <c r="J28" s="47">
         <f>AVERAGE(Q28:T28)</f>
         <v>-0.43920105916112662</v>
       </c>
-      <c r="K28" s="55">
+      <c r="K28" s="47">
         <f>MAX(Q28:T28)</f>
         <v>-0.39580845178592533</v>
       </c>
-      <c r="L28" s="55">
+      <c r="L28" s="47">
         <f>MIN(Q28:T28)</f>
         <v>-0.47411805352677838</v>
       </c>
-      <c r="M28" s="49">
+      <c r="M28" s="43">
         <v>-30</v>
       </c>
-      <c r="N28" s="49">
+      <c r="N28" s="43">
         <v>-30</v>
       </c>
-      <c r="O28" s="49">
+      <c r="O28" s="43">
         <v>-30</v>
       </c>
-      <c r="P28" s="49">
+      <c r="P28" s="43">
         <v>-30</v>
       </c>
-      <c r="Q28" s="48">
+      <c r="Q28" s="42">
         <f>M28/Fig2Fig3Context!F47</f>
         <v>-0.43242640386118403</v>
       </c>
-      <c r="R28" s="48">
+      <c r="R28" s="42">
         <f>N28/Fig2Fig3Context!G47</f>
         <v>-0.47411805352677838</v>
       </c>
-      <c r="S28" s="48">
+      <c r="S28" s="42">
         <f>O28/Fig2Fig3Context!H47</f>
         <v>-0.39580845178592533</v>
       </c>
-      <c r="T28" s="48">
+      <c r="T28" s="42">
         <f>P28/Fig2Fig3Context!I47</f>
         <v>-0.45445132747061878</v>
       </c>
-      <c r="U28" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="V28" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W28" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
+      <c r="U28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" t="s">
         <v>212</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" t="s">
         <v>292</v>
       </c>
-      <c r="D29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="47">
-        <f>U29</f>
+      <c r="D29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" ref="G29:G42" si="6">U29</f>
         <v>-30</v>
       </c>
-      <c r="H29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J29" s="55">
+      <c r="H29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J29" s="47">
         <f>U29/Fig2Fig3Context!F24</f>
         <v>-0.65217391304347827</v>
       </c>
-      <c r="K29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U29" s="47">
+      <c r="K29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U29" s="3">
         <v>-30</v>
       </c>
-      <c r="V29" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W29" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="V29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>200</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" t="s">
         <v>211</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" t="s">
         <v>175</v>
       </c>
-      <c r="D30" s="49">
+      <c r="D30" s="43">
         <v>66.3</v>
       </c>
-      <c r="E30" s="48">
+      <c r="E30" s="42">
         <f>D30/Fig2Fig3Context!F17</f>
         <v>4.4214738246082026E-2</v>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="43">
         <v>12</v>
       </c>
-      <c r="G30" s="49">
-        <f>U30</f>
+      <c r="G30" s="43">
+        <f t="shared" si="6"/>
         <v>103.83799999999999</v>
       </c>
-      <c r="H30" s="49">
-        <f>V30</f>
+      <c r="H30" s="43">
+        <f t="shared" ref="H30:I34" si="7">V30</f>
         <v>130.59690000000001</v>
       </c>
-      <c r="I30" s="49">
-        <f>W30</f>
+      <c r="I30" s="43">
+        <f t="shared" si="7"/>
         <v>86.041480000000007</v>
       </c>
-      <c r="J30" s="48">
+      <c r="J30" s="42">
         <f>U30/Fig2Fig3Context!$F$29</f>
         <v>6.5866159213447503E-2</v>
       </c>
-      <c r="K30" s="48">
+      <c r="K30" s="42">
         <f>V30/Fig2Fig3Context!$F$29</f>
         <v>8.2839771646051386E-2</v>
       </c>
-      <c r="L30" s="48">
+      <c r="L30" s="42">
         <f>W30/Fig2Fig3Context!$F$29</f>
         <v>5.4577532508721854E-2</v>
       </c>
-      <c r="M30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T30" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U30" s="49">
+      <c r="M30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U30" s="43">
         <v>103.83799999999999</v>
       </c>
-      <c r="V30" s="49">
+      <c r="V30" s="43">
         <v>130.59690000000001</v>
       </c>
-      <c r="W30" s="49">
+      <c r="W30" s="43">
         <v>86.041480000000007</v>
       </c>
-      <c r="X30" s="58"/>
-      <c r="Y30" s="58"/>
-    </row>
-    <row r="31" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>200</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="43">
         <v>43.5</v>
       </c>
-      <c r="E31" s="48">
+      <c r="E31" s="42">
         <f>D31/Fig2Fig3Context!F18</f>
         <v>6.7441860465116285E-2</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="43">
         <v>12</v>
       </c>
-      <c r="G31" s="49">
-        <f>U31</f>
+      <c r="G31" s="43">
+        <f t="shared" si="6"/>
         <v>143.0462</v>
       </c>
-      <c r="H31" s="49">
-        <f>V31</f>
+      <c r="H31" s="43">
+        <f t="shared" si="7"/>
         <v>184.20310000000001</v>
       </c>
-      <c r="I31" s="49">
-        <f>W31</f>
+      <c r="I31" s="43">
+        <f t="shared" si="7"/>
         <v>117.0497</v>
       </c>
-      <c r="J31" s="48">
+      <c r="J31" s="42">
         <f>U31/Fig2Fig3Context!$F$30</f>
         <v>0.22960866773675762</v>
       </c>
-      <c r="K31" s="48">
+      <c r="K31" s="42">
         <f>V31/Fig2Fig3Context!$F$30</f>
         <v>0.29567110754414128</v>
       </c>
-      <c r="L31" s="48">
+      <c r="L31" s="42">
         <f>W31/Fig2Fig3Context!$F$30</f>
         <v>0.18788073836276084</v>
       </c>
-      <c r="M31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U31" s="49">
+      <c r="M31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U31" s="43">
         <v>143.0462</v>
       </c>
-      <c r="V31" s="49">
+      <c r="V31" s="43">
         <v>184.20310000000001</v>
       </c>
-      <c r="W31" s="49">
+      <c r="W31" s="43">
         <v>117.0497</v>
       </c>
-      <c r="X31" s="58"/>
-      <c r="Y31" s="58"/>
-    </row>
-    <row r="32" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" t="s">
         <v>209</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" t="s">
         <v>175</v>
       </c>
-      <c r="D32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="49">
-        <f>U32</f>
+      <c r="D32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="43">
+        <f t="shared" si="6"/>
         <v>129.03309999999999</v>
       </c>
-      <c r="H32" s="49">
-        <f>V32</f>
+      <c r="H32" s="43">
+        <f t="shared" si="7"/>
         <v>216.036</v>
       </c>
-      <c r="I32" s="49">
-        <f>W32</f>
+      <c r="I32" s="43">
+        <f t="shared" si="7"/>
         <v>92.827979999999997</v>
       </c>
-      <c r="J32" s="48">
+      <c r="J32" s="42">
         <f>U32/Fig2Fig3Context!$F$27</f>
         <v>0.2952702517162471</v>
       </c>
-      <c r="K32" s="48">
+      <c r="K32" s="42">
         <f>V32/Fig2Fig3Context!$F$27</f>
         <v>0.49436155606407323</v>
       </c>
-      <c r="L32" s="48">
+      <c r="L32" s="42">
         <f>W32/Fig2Fig3Context!$F$27</f>
         <v>0.21242100686498855</v>
       </c>
-      <c r="M32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T32" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U32" s="49">
+      <c r="M32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U32" s="43">
         <v>129.03309999999999</v>
       </c>
-      <c r="V32" s="49">
+      <c r="V32" s="43">
         <v>216.036</v>
       </c>
-      <c r="W32" s="49">
+      <c r="W32" s="43">
         <v>92.827979999999997</v>
       </c>
-      <c r="X32" s="58"/>
-      <c r="Y32" s="58"/>
-    </row>
-    <row r="33" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>200</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" t="s">
         <v>175</v>
       </c>
-      <c r="D33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G33" s="49">
-        <f>U33</f>
+      <c r="D33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="43">
+        <f t="shared" si="6"/>
         <v>175.29859999999999</v>
       </c>
-      <c r="H33" s="49">
-        <f>V33</f>
+      <c r="H33" s="43">
+        <f t="shared" si="7"/>
         <v>277.17970000000003</v>
       </c>
-      <c r="I33" s="49">
-        <f>W33</f>
+      <c r="I33" s="43">
+        <f t="shared" si="7"/>
         <v>128.12029999999999</v>
       </c>
-      <c r="J33" s="48">
+      <c r="J33" s="42">
         <f>U33/Fig2Fig3Context!$F$28</f>
         <v>0.63861056466302368</v>
       </c>
-      <c r="K33" s="48">
+      <c r="K33" s="42">
         <f>V33/Fig2Fig3Context!$F$28</f>
         <v>1.0097621129326049</v>
       </c>
-      <c r="L33" s="48">
+      <c r="L33" s="42">
         <f>W33/Fig2Fig3Context!$F$28</f>
         <v>0.46674061930783239</v>
       </c>
-      <c r="M33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T33" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U33" s="49">
+      <c r="M33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U33" s="43">
         <v>175.29859999999999</v>
       </c>
-      <c r="V33" s="49">
+      <c r="V33" s="43">
         <v>277.17970000000003</v>
       </c>
-      <c r="W33" s="49">
+      <c r="W33" s="43">
         <v>128.12029999999999</v>
       </c>
-      <c r="X33" s="58"/>
-      <c r="Y33" s="58"/>
-    </row>
-    <row r="34" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>200</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" t="s">
         <v>207</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" t="s">
         <v>175</v>
       </c>
-      <c r="D34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G34" s="49">
-        <f>U34</f>
+      <c r="D34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="43">
+        <f t="shared" si="6"/>
         <v>152.03569999999999</v>
       </c>
-      <c r="H34" s="49">
-        <f>V34</f>
+      <c r="H34" s="43">
+        <f t="shared" si="7"/>
         <v>169.08199999999999</v>
       </c>
-      <c r="I34" s="49">
-        <f>W34</f>
+      <c r="I34" s="43">
+        <f t="shared" si="7"/>
         <v>137.80199999999999</v>
       </c>
-      <c r="J34" s="48">
+      <c r="J34" s="42">
         <f>U34/Fig2Fig3Context!$F$25</f>
         <v>0.35563906432748538</v>
       </c>
-      <c r="K34" s="48">
+      <c r="K34" s="42">
         <f>V34/Fig2Fig3Context!$F$25</f>
         <v>0.39551345029239765</v>
       </c>
-      <c r="L34" s="48">
+      <c r="L34" s="42">
         <f>W34/Fig2Fig3Context!$F$25</f>
         <v>0.32234385964912277</v>
       </c>
-      <c r="M34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T34" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U34" s="49">
+      <c r="M34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U34" s="43">
         <v>152.03569999999999</v>
       </c>
-      <c r="V34" s="49">
+      <c r="V34" s="43">
         <v>169.08199999999999</v>
       </c>
-      <c r="W34" s="49">
+      <c r="W34" s="43">
         <v>137.80199999999999</v>
       </c>
-      <c r="X34" s="58"/>
-      <c r="Y34" s="58"/>
-    </row>
-    <row r="35" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+      <c r="X34" s="50"/>
+      <c r="Y34" s="50"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" t="s">
         <v>206</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="49">
+      <c r="D35" s="43">
         <v>0</v>
       </c>
-      <c r="E35" s="48">
+      <c r="E35" s="42">
         <f>D35/Fig2Fig3Context!F19</f>
         <v>0</v>
       </c>
-      <c r="F35" s="47" t="s">
+      <c r="F35" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G35" s="49">
-        <f>U35</f>
+      <c r="G35" s="43">
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
-      <c r="H35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J35" s="48">
+      <c r="H35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="42">
         <f>U35/Fig2Fig3Context!$F$31</f>
         <v>0.1971050200184786</v>
       </c>
-      <c r="K35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U35" s="49">
+      <c r="K35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U35" s="43">
         <v>320</v>
       </c>
-      <c r="V35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W35" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X35" s="58"/>
-      <c r="Y35" s="58"/>
-    </row>
-    <row r="36" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="V35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X35" s="50"/>
+      <c r="Y35" s="50"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>200</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" t="s">
         <v>204</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" t="s">
         <v>175</v>
       </c>
-      <c r="D36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G36" s="49">
-        <f>U36</f>
+      <c r="D36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="43">
+        <f t="shared" si="6"/>
         <v>338.55610000000001</v>
       </c>
-      <c r="H36" s="49">
-        <f>V36</f>
+      <c r="H36" s="43">
+        <f t="shared" ref="H36:I40" si="8">V36</f>
         <v>541.37059999999997</v>
       </c>
-      <c r="I36" s="49">
-        <f>W36</f>
+      <c r="I36" s="43">
+        <f t="shared" si="8"/>
         <v>246.63560000000001</v>
       </c>
-      <c r="J36" s="48">
+      <c r="J36" s="42">
         <f>U36/Fig2Fig3Context!$F$26</f>
         <v>0.80036903073286059</v>
       </c>
-      <c r="K36" s="48">
+      <c r="K36" s="42">
         <f>V36/Fig2Fig3Context!$F$26</f>
         <v>1.2798359338061465</v>
       </c>
-      <c r="L36" s="48">
+      <c r="L36" s="42">
         <f>W36/Fig2Fig3Context!$F$26</f>
         <v>0.58306288416075658</v>
       </c>
-      <c r="M36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T36" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U36" s="49">
+      <c r="M36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U36" s="43">
         <v>338.55610000000001</v>
       </c>
-      <c r="V36" s="49">
+      <c r="V36" s="43">
         <v>541.37059999999997</v>
       </c>
-      <c r="W36" s="49">
+      <c r="W36" s="43">
         <v>246.63560000000001</v>
       </c>
-      <c r="X36" s="58"/>
-      <c r="Y36" s="58"/>
-    </row>
-    <row r="37" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="X36" s="50"/>
+      <c r="Y36" s="50"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>200</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" t="s">
         <v>203</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" t="s">
         <v>175</v>
       </c>
-      <c r="D37" s="49">
+      <c r="D37" s="43">
         <v>180</v>
       </c>
-      <c r="E37" s="48">
+      <c r="E37" s="42">
         <f>D37/Fig2Fig3Context!F19</f>
         <v>0.11087157376039421</v>
       </c>
-      <c r="F37" s="47">
+      <c r="F37" s="3">
         <v>13</v>
       </c>
-      <c r="G37" s="49">
-        <f>U37</f>
+      <c r="G37" s="43">
+        <f t="shared" si="6"/>
         <v>904</v>
       </c>
-      <c r="H37" s="49">
-        <f>V37</f>
+      <c r="H37" s="43">
+        <f t="shared" si="8"/>
         <v>1371</v>
       </c>
-      <c r="I37" s="49">
-        <f>W37</f>
+      <c r="I37" s="43">
+        <f t="shared" si="8"/>
         <v>675</v>
       </c>
-      <c r="J37" s="48">
+      <c r="J37" s="42">
         <f>U37/Fig2Fig3Context!$F$31</f>
         <v>0.55682168155220202</v>
       </c>
-      <c r="K37" s="48">
+      <c r="K37" s="42">
         <f>V37/Fig2Fig3Context!$F$31</f>
         <v>0.84447182014166922</v>
       </c>
-      <c r="L37" s="48">
+      <c r="L37" s="42">
         <f>W37/Fig2Fig3Context!$F$31</f>
         <v>0.41576840160147827</v>
       </c>
-      <c r="M37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T37" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U37" s="49">
+      <c r="M37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U37" s="43">
         <v>904</v>
       </c>
-      <c r="V37" s="49">
+      <c r="V37" s="43">
         <v>1371</v>
       </c>
-      <c r="W37" s="49">
+      <c r="W37" s="43">
         <v>675</v>
       </c>
-      <c r="X37" s="57"/>
-    </row>
-    <row r="38" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="X37" s="49"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>200</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" t="s">
         <v>202</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" t="s">
         <v>198</v>
       </c>
-      <c r="D38" s="49">
+      <c r="D38" s="43">
         <v>12.85</v>
       </c>
-      <c r="E38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F38" s="47">
+      <c r="E38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="3">
         <v>12</v>
       </c>
-      <c r="G38" s="52">
-        <f>U38</f>
+      <c r="G38" s="4">
+        <f t="shared" si="6"/>
         <v>-4.9783379999999999</v>
       </c>
-      <c r="H38" s="52">
-        <f>V38</f>
+      <c r="H38" s="4">
+        <f t="shared" si="8"/>
         <v>-4.4934839999999996</v>
       </c>
-      <c r="I38" s="52">
-        <f>W38</f>
+      <c r="I38" s="4">
+        <f t="shared" si="8"/>
         <v>-5.5775430000000004</v>
       </c>
-      <c r="J38" s="48">
+      <c r="J38" s="42">
         <f>U38/$D$38</f>
         <v>-0.38741929961089494</v>
       </c>
-      <c r="K38" s="48">
+      <c r="K38" s="42">
         <f>V38/$D$38</f>
         <v>-0.34968747081712059</v>
       </c>
-      <c r="L38" s="48">
+      <c r="L38" s="42">
         <f>W38/$D$38</f>
         <v>-0.43405003891050586</v>
       </c>
-      <c r="M38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T38" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U38" s="52">
+      <c r="M38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U38" s="4">
         <v>-4.9783379999999999</v>
       </c>
-      <c r="V38" s="52">
+      <c r="V38" s="4">
         <v>-4.4934839999999996</v>
       </c>
-      <c r="W38" s="52">
+      <c r="W38" s="4">
         <v>-5.5775430000000004</v>
       </c>
-      <c r="X38" s="57"/>
-    </row>
-    <row r="39" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+      <c r="X38" s="49"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>200</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" t="s">
         <v>201</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" t="s">
         <v>175</v>
       </c>
-      <c r="D39" s="47">
+      <c r="D39" s="3">
         <v>20.3</v>
       </c>
-      <c r="E39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F39" s="47">
+      <c r="E39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="3">
         <v>14</v>
       </c>
-      <c r="G39" s="52">
-        <f>U39</f>
+      <c r="G39" s="4">
+        <f t="shared" si="6"/>
         <v>18.042159999999999</v>
       </c>
-      <c r="H39" s="52">
-        <f>V39</f>
+      <c r="H39" s="4">
+        <f t="shared" si="8"/>
         <v>45.233789999999999</v>
       </c>
-      <c r="I39" s="52">
-        <f>W39</f>
+      <c r="I39" s="4">
+        <f t="shared" si="8"/>
         <v>11.192539999999999</v>
       </c>
-      <c r="J39" s="48">
+      <c r="J39" s="42">
         <f>U39/$D$39</f>
         <v>0.88877635467980287</v>
       </c>
-      <c r="K39" s="48">
+      <c r="K39" s="42">
         <f>V39/$D$39</f>
         <v>2.228265517241379</v>
       </c>
-      <c r="L39" s="48">
+      <c r="L39" s="42">
         <f>W39/$D$39</f>
         <v>0.55135665024630531</v>
       </c>
-      <c r="M39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U39" s="52">
+      <c r="M39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U39" s="4">
         <v>18.042159999999999</v>
       </c>
-      <c r="V39" s="52">
+      <c r="V39" s="4">
         <v>45.233789999999999</v>
       </c>
-      <c r="W39" s="52">
+      <c r="W39" s="4">
         <v>11.192539999999999</v>
       </c>
-      <c r="X39" s="57"/>
-    </row>
-    <row r="40" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+      <c r="X39" s="49"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>200</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" t="s">
         <v>198</v>
       </c>
-      <c r="D40" s="47">
+      <c r="D40" s="3">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40" s="47">
+      <c r="E40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="3">
         <v>15</v>
       </c>
-      <c r="G40" s="52">
-        <f>U40</f>
+      <c r="G40" s="4">
+        <f t="shared" si="6"/>
         <v>-0.54721779999999998</v>
       </c>
-      <c r="H40" s="52">
-        <f>V40</f>
+      <c r="H40" s="4">
+        <f t="shared" si="8"/>
         <v>-0.35146769999999999</v>
       </c>
-      <c r="I40" s="52">
-        <f>W40</f>
+      <c r="I40" s="4">
+        <f t="shared" si="8"/>
         <v>-1.2115610000000001</v>
       </c>
-      <c r="J40" s="48">
+      <c r="J40" s="42">
         <f>U40/$D$40</f>
         <v>-0.96003122807017549</v>
       </c>
-      <c r="K40" s="48">
+      <c r="K40" s="42">
         <f>V40/$D$40</f>
         <v>-0.61660999999999999</v>
       </c>
-      <c r="L40" s="48">
+      <c r="L40" s="42">
         <f>W40/$D$40</f>
         <v>-2.1255456140350879</v>
       </c>
-      <c r="M40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T40" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U40" s="52">
+      <c r="M40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U40" s="4">
         <v>-0.54721779999999998</v>
       </c>
-      <c r="V40" s="52">
+      <c r="V40" s="4">
         <v>-0.35146769999999999</v>
       </c>
-      <c r="W40" s="52">
+      <c r="W40" s="4">
         <v>-1.2115610000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" t="s">
         <v>197</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" t="s">
         <v>196</v>
       </c>
-      <c r="D41" s="49">
+      <c r="D41" s="43">
         <v>360.12</v>
       </c>
-      <c r="E41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F41" s="47">
+      <c r="E41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41" s="3">
         <v>7</v>
       </c>
-      <c r="G41" s="49">
-        <f>U41</f>
-        <v>-110</v>
-      </c>
-      <c r="H41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J41" s="48">
+      <c r="G41" s="43">
+        <f t="shared" si="6"/>
+        <v>-125.61929984252112</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J41" s="54">
         <f>U41/Fig2Fig3Context!F32</f>
-        <v>-0.27572692009732708</v>
-      </c>
-      <c r="K41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U41" s="49">
-        <v>-110</v>
-      </c>
-      <c r="V41" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W41" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+        <v>-0.31487838773055449</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U41" s="43">
+        <v>-125.61929984252112</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>195</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" t="s">
         <v>194</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" t="s">
         <v>151</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="4">
         <f>2030.97181059712/1000</f>
         <v>2.0309718105971202</v>
       </c>
-      <c r="E42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="47">
+      <c r="E42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" s="3">
         <v>8</v>
       </c>
-      <c r="G42" s="52">
-        <f>U42</f>
+      <c r="G42" s="4">
+        <f t="shared" si="6"/>
         <v>1.3826935245836804</v>
       </c>
-      <c r="H42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J42" s="48">
-        <f>U42/Fig2Fig3Context!F33</f>
-        <v>0.50842181915714113</v>
-      </c>
-      <c r="K42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="L42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="M42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="N42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="O42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="P42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="R42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="T42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U42" s="52">
+      <c r="H42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J42" s="42">
+        <f>-U42/Fig2Fig3Context!F33</f>
+        <v>-0.50842181915714113</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U42" s="4">
         <v>1.3826935245836804</v>
       </c>
-      <c r="V42" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="W42" s="47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:25" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="49" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="51" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="53" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="54" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="V42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7436,887 +7419,876 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55957D73-D054-4810-8ADC-EB34ECBC3453}">
-  <dimension ref="B1:J72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:J69"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="17"/>
-    <col min="2" max="2" width="2.85546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="50.5703125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="17"/>
+    <col min="2" max="2" width="2.81640625" customWidth="1"/>
+    <col min="3" max="3" width="50.54296875" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B1" s="16"/>
     </row>
-    <row r="2" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="18" t="s">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C5" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="19" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="21" t="s">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C6" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6">
         <v>2024</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>30914.83</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="21" t="s">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C7" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7">
         <v>2023</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" t="s">
         <v>169</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>97</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="21" t="s">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C8" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8">
         <v>2020</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="23">
         <v>69.485960340752513</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="21" t="s">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C9" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9">
         <v>2020</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" t="s">
         <v>154</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <v>11050.227144381759</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="24">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="21" t="s">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C10" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10">
         <v>2020</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" t="s">
         <v>190</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <v>906.95725093600004</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="24">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="21" t="s">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C11" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11">
         <v>2020</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="23">
         <v>2.1795505374233453</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="24">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="21" t="s">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C12" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12">
         <v>2020</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="23">
         <v>4.3625501270486513</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="24">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="21" t="s">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C13" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" t="s">
         <v>175</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <v>369</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="21" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C14" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" t="s">
         <v>175</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <v>421</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="21" t="s">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C15" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <v>417</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="21" t="s">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C16" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" t="s">
         <v>175</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>285</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="21" t="s">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C17" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" t="s">
         <v>175</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <v>1499.5</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="21" t="s">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C18" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" t="s">
         <v>175</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="21">
         <v>645</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="27" t="s">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C19" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="28">
         <v>1623.5</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="29">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="22"/>
-    </row>
-    <row r="21" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F20" s="21"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" s="7" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="18" t="s">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C23" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="19" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="2:10" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="C24" s="21" t="s">
+    <row r="24" spans="2:10" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C24" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24">
         <v>2050</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" t="s">
         <v>290</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="21">
         <v>46</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="24">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="21" t="s">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C25" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25">
         <v>2050</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" t="s">
         <v>175</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="21">
         <v>427.5</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="21" t="s">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C26" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26">
         <v>2050</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" t="s">
         <v>175</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="21">
         <v>423</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="21" t="s">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C27" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27">
         <v>2050</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" t="s">
         <v>175</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="21">
         <v>437</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="21" t="s">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C28" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28">
         <v>2050</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" t="s">
         <v>175</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="21">
         <v>274.5</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="21" t="s">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C29" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29">
         <v>2050</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" t="s">
         <v>175</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="21">
         <v>1576.5</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="21" t="s">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C30" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30">
         <v>2050</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" t="s">
         <v>175</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="21">
         <v>623</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="24">
         <v>5</v>
       </c>
-      <c r="J30" s="33"/>
-    </row>
-    <row r="31" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="21" t="s">
+      <c r="J30" s="31"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C31" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31">
         <v>2050</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" t="s">
         <v>175</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="21">
         <v>1623.5</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="21" t="s">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C32" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32">
         <v>2050</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" t="s">
         <v>173</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="21">
         <v>398.94544921900189</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="24">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="21" t="s">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C33" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33">
         <v>2050</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" t="s">
         <v>151</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="23">
         <v>2.7195794367674897</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="24">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="21" t="s">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C34" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34">
         <v>2050</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" t="s">
         <v>169</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="21">
         <v>200</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="24">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="27" t="s">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C35" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="27">
         <v>2050</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="28">
         <v>600</v>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="29">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F36" s="22"/>
-    </row>
-    <row r="37" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B37" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="F37" s="22"/>
-    </row>
-    <row r="38" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F39" s="34" t="s">
+      <c r="F37" s="21"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F39" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="36"/>
-    </row>
-    <row r="40" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="18" t="s">
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="53"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C40" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F40" s="37" t="s">
+      <c r="F40" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="G40" s="38" t="s">
+      <c r="G40" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="H40" s="38" t="s">
+      <c r="H40" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="I40" s="39" t="s">
+      <c r="I40" s="34" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="21" t="s">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C41" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41">
         <v>2050</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" t="s">
         <v>154</v>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="35">
         <v>43833.923133164892</v>
       </c>
-      <c r="G41" s="40">
+      <c r="G41" s="35">
         <v>41665.736086158518</v>
       </c>
-      <c r="H41" s="40">
+      <c r="H41" s="35">
         <v>61617.455072704513</v>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="36">
         <v>34405.716184003606</v>
       </c>
     </row>
-    <row r="42" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="21" t="s">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C42" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42">
         <v>2050</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" t="s">
         <v>154</v>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="35">
         <v>104.75817043097416</v>
       </c>
-      <c r="G42" s="40">
+      <c r="G42" s="35">
         <v>104.7581704309742</v>
       </c>
-      <c r="H42" s="40">
+      <c r="H42" s="35">
         <v>123.25860962212907</v>
       </c>
-      <c r="I42" s="41">
+      <c r="I42" s="36">
         <v>111.30211817130605</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="21" t="s">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C43" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43">
         <v>2050</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" t="s">
         <v>156</v>
       </c>
-      <c r="F43" s="40">
+      <c r="F43" s="35">
         <v>11.62</v>
       </c>
-      <c r="G43" s="40">
+      <c r="G43" s="35">
         <v>11.62</v>
       </c>
-      <c r="H43" s="40">
+      <c r="H43" s="35">
         <v>25.9</v>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="36">
         <v>19.239999999999998</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="21" t="s">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C44" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44">
         <v>2050</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" t="s">
         <v>154</v>
       </c>
-      <c r="F44" s="40">
+      <c r="F44" s="35">
         <v>15104.882101872166</v>
       </c>
-      <c r="G44" s="40">
+      <c r="G44" s="35">
         <v>14691.286953140809</v>
       </c>
-      <c r="H44" s="40">
+      <c r="H44" s="35">
         <v>17503.343261838108</v>
       </c>
-      <c r="I44" s="41">
+      <c r="I44" s="36">
         <v>9796.5494007005873</v>
       </c>
     </row>
-    <row r="45" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="21" t="s">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C45" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45">
         <v>2050</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" t="s">
         <v>151</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="23">
         <v>3.1778498279578726</v>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="23">
         <v>3.1125798929048347</v>
       </c>
-      <c r="H45" s="24">
+      <c r="H45" s="23">
         <v>4.2905098431786142</v>
       </c>
-      <c r="I45" s="42">
+      <c r="I45" s="37">
         <v>2.8900105021101643</v>
       </c>
     </row>
-    <row r="46" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="21" t="s">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C46" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46">
         <v>2050</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" t="s">
         <v>151</v>
       </c>
-      <c r="F46" s="43">
+      <c r="F46" s="38">
         <v>4.7409568368258723</v>
       </c>
-      <c r="G46" s="43">
+      <c r="G46" s="38">
         <v>4.595203630999297</v>
       </c>
-      <c r="H46" s="43">
+      <c r="H46" s="38">
         <v>7.819488123387198</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="39">
         <v>5.133683640425728</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="C47" s="21" t="s">
+    <row r="47" spans="2:9" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C47" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="26" t="s">
+      <c r="D47" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" t="s">
         <v>290</v>
       </c>
-      <c r="F47" s="43">
+      <c r="F47" s="38">
         <v>69.375967175284913</v>
       </c>
-      <c r="G47" s="43">
+      <c r="G47" s="38">
         <v>63.275379996272569</v>
       </c>
-      <c r="H47" s="43">
+      <c r="H47" s="38">
         <v>75.794238007392593</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="39">
         <v>66.013670082060798</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="C48" s="27" t="s">
+    <row r="48" spans="2:9" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C48" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="27">
         <v>2050</v>
       </c>
-      <c r="E48" s="29" t="s">
+      <c r="E48" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="F48" s="45">
+      <c r="F48" s="40">
         <v>5.2487469999999998</v>
       </c>
-      <c r="G48" s="45">
+      <c r="G48" s="40">
         <v>4.5999670000000004</v>
       </c>
-      <c r="H48" s="45">
+      <c r="H48" s="40">
         <v>7.0066639999999998</v>
       </c>
-      <c r="I48" s="46">
+      <c r="I48" s="41">
         <v>5.7998539999999998</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-    </row>
-    <row r="50" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B51" s="7" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="52" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="17">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B52">
         <v>1</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="17">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B53">
         <v>2</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="54" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="17">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B54">
         <v>3</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="55" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="17">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B55">
         <v>4</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="56" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="17">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B56">
         <v>5</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="17">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B57">
         <v>6</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="17">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B58">
         <v>7</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="17">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B59">
         <v>8</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="60" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="17">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B60">
         <v>9</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="17">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B61">
         <v>10</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="62" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="17">
-        <v>11</v>
-      </c>
-      <c r="C62" s="17" t="s">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B62">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="17">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B63">
         <v>12</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="64" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="17">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B64">
         <v>13</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="65" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="17">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B65">
         <v>14</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="66" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="17">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B66">
         <v>15</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B68" s="7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="17" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
         <v>130</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:3" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="F39:I39"/>
@@ -8328,16 +8300,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46FE443-F0A2-4AF4-B019-88A424862813}">
   <dimension ref="A1:P241"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="8.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="16" width="8.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="7" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
@@ -8387,7 +8359,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -8437,7 +8409,7 @@
         <v>8.6032406347629191</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -8487,7 +8459,7 @@
         <v>5.8999752059009802</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -8537,7 +8509,7 @@
         <v>3.1264515631028802</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -8587,7 +8559,7 @@
         <v>3.1264230134144899</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -8637,7 +8609,7 @@
         <v>1.31304295778447</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>69</v>
       </c>
@@ -8687,7 +8659,7 @@
         <v>4.7329457054553101</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>69</v>
       </c>
@@ -8737,7 +8709,7 @@
         <v>4.3557806559817198</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -8787,7 +8759,7 @@
         <v>1.88910431365378</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -8837,7 +8809,7 @@
         <v>1.1166591764176601</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -8887,7 +8859,7 @@
         <v>0.67500681161110698</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -8937,7 +8909,7 @@
         <v>0.14962067068005699</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -8987,7 +8959,7 @@
         <v>0.77567952651425598</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -9037,7 +9009,7 @@
         <v>0.56375269610183498</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -9087,7 +9059,7 @@
         <v>1.2894233639949699</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -9137,7 +9109,7 @@
         <v>1.0786100724523799</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -9187,7 +9159,7 @@
         <v>0.78503636743281802</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -9237,7 +9209,7 @@
         <v>0.61227693993387899</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -9287,7 +9259,7 @@
         <v>0.53765587095914902</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -9337,7 +9309,7 @@
         <v>1.4698045325282101</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -9387,7 +9359,7 @@
         <v>0.80519439161553996</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -9437,7 +9409,7 @@
         <v>0.41680012607359102</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -9487,7 +9459,7 @@
         <v>0.44566469530619801</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>73</v>
       </c>
@@ -9537,7 +9509,7 @@
         <v>0.29417249191220401</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>73</v>
       </c>
@@ -9587,7 +9559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -9637,7 +9609,7 @@
         <v>9.9519865134392802</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -9687,7 +9659,7 @@
         <v>4.4346474539939402</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -9737,7 +9709,7 @@
         <v>2.4270400894045099</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -9787,7 +9759,7 @@
         <v>3.5171872038015302</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -9837,7 +9809,7 @@
         <v>1.05603674196088</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -9887,7 +9859,7 @@
         <v>4.5094211617255997</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -9937,7 +9909,7 @@
         <v>4.49467266194244</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>71</v>
       </c>
@@ -9987,7 +9959,7 @@
         <v>1.03740161382296</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -10037,7 +10009,7 @@
         <v>3.7253452986500202</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -10087,7 +10059,7 @@
         <v>1.0511598260327599</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -10137,7 +10109,7 @@
         <v>0.98614329023512604</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -10187,7 +10159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -10237,7 +10209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -10287,7 +10259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>71</v>
       </c>
@@ -10337,7 +10309,7 @@
         <v>0.63610536729701495</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>71</v>
       </c>
@@ -10387,7 +10359,7 @@
         <v>0.38738705141664898</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>71</v>
       </c>
@@ -10437,7 +10409,7 @@
         <v>0.27047181667247799</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -10487,7 +10459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -10537,7 +10509,7 @@
         <v>2.1969768061531001</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>71</v>
       </c>
@@ -10587,7 +10559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>71</v>
       </c>
@@ -10637,7 +10609,7 @@
         <v>0.46842234636528202</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>71</v>
       </c>
@@ -10687,7 +10659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>71</v>
       </c>
@@ -10737,7 +10709,7 @@
         <v>0.32183493594207402</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>71</v>
       </c>
@@ -10787,7 +10759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>71</v>
       </c>
@@ -10837,7 +10809,7 @@
         <v>9.8967381173710898</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -10887,7 +10859,7 @@
         <v>6.1351983940550401</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -10937,7 +10909,7 @@
         <v>2.44747403706539</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>71</v>
       </c>
@@ -10987,7 +10959,7 @@
         <v>1.05318621561334</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>71</v>
       </c>
@@ -11037,7 +11009,7 @@
         <v>1.1413917976225301</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>71</v>
       </c>
@@ -11087,7 +11059,7 @@
         <v>3.2845368564295199</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>71</v>
       </c>
@@ -11137,7 +11109,7 @@
         <v>2.8437177938069498</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -11187,7 +11159,7 @@
         <v>4.6424095130425904</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -11237,7 +11209,7 @@
         <v>3.4958910724175398</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>71</v>
       </c>
@@ -11287,7 +11259,7 @@
         <v>1.4847675133806499</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>71</v>
       </c>
@@ -11337,7 +11309,7 @@
         <v>1.76295395874586</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>71</v>
       </c>
@@ -11387,7 +11359,7 @@
         <v>4.2909568837801497E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -11437,7 +11409,7 @@
         <v>5.6919837616064901E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -11487,7 +11459,7 @@
         <v>8.2158886449792995E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -11537,7 +11509,7 @@
         <v>1.02363049603946</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>71</v>
       </c>
@@ -11587,7 +11559,7 @@
         <v>0.238373465139741</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -11637,7 +11609,7 @@
         <v>0.155068049106522</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -11687,7 +11659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -11737,7 +11709,7 @@
         <v>0.74621638920468703</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -11787,7 +11759,7 @@
         <v>0.82928574416579903</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -11837,7 +11809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -11887,7 +11859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -11937,7 +11909,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>71</v>
       </c>
@@ -11987,7 +11959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>71</v>
       </c>
@@ -12037,7 +12009,7 @@
         <v>5.7273946170978798</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>71</v>
       </c>
@@ -12087,7 +12059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>71</v>
       </c>
@@ -12137,7 +12109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>71</v>
       </c>
@@ -12187,7 +12159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>71</v>
       </c>
@@ -12237,7 +12209,7 @@
         <v>1.2513058037932501</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>71</v>
       </c>
@@ -12287,7 +12259,7 @@
         <v>2.52408876123677</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>71</v>
       </c>
@@ -12337,7 +12309,7 @@
         <v>1.9352846021504599</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>71</v>
       </c>
@@ -12387,7 +12359,7 @@
         <v>0.483177955820425</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -12437,7 +12409,7 @@
         <v>0.63921143218627696</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>71</v>
       </c>
@@ -12487,7 +12459,7 @@
         <v>0.76258940322272295</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>71</v>
       </c>
@@ -12537,7 +12509,7 @@
         <v>0.310214043677975</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>71</v>
       </c>
@@ -12587,7 +12559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>71</v>
       </c>
@@ -12637,7 +12609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>71</v>
       </c>
@@ -12687,7 +12659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>71</v>
       </c>
@@ -12737,7 +12709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>71</v>
       </c>
@@ -12787,7 +12759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>71</v>
       </c>
@@ -12837,7 +12809,7 @@
         <v>0.34088239889358202</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>71</v>
       </c>
@@ -12887,7 +12859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>71</v>
       </c>
@@ -12937,7 +12909,7 @@
         <v>0.25025532185988503</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -12987,7 +12959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>71</v>
       </c>
@@ -13037,7 +13009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>71</v>
       </c>
@@ -13087,7 +13059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>71</v>
       </c>
@@ -13137,7 +13109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="8" t="s">
         <v>71</v>
       </c>
@@ -13187,7 +13159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>71</v>
       </c>
@@ -13237,7 +13209,7 @@
         <v>11.4136443056923</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>71</v>
       </c>
@@ -13287,7 +13259,7 @@
         <v>5.60457550063607</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>71</v>
       </c>
@@ -13337,7 +13309,7 @@
         <v>3.0570005250557002</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>71</v>
       </c>
@@ -13387,7 +13359,7 @@
         <v>2.1595263518114698</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>71</v>
       </c>
@@ -13437,7 +13409,7 @@
         <v>1.0662543570687699</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>71</v>
       </c>
@@ -13487,7 +13459,7 @@
         <v>1.6171759767226801</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>71</v>
       </c>
@@ -13537,7 +13509,7 @@
         <v>2.38507619444264</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>71</v>
       </c>
@@ -13587,7 +13559,7 @@
         <v>1.46915897495922</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>71</v>
       </c>
@@ -13637,7 +13609,7 @@
         <v>3.2532536635397502</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>71</v>
       </c>
@@ -13687,7 +13659,7 @@
         <v>1.4701890104777899</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>71</v>
       </c>
@@ -13737,7 +13709,7 @@
         <v>0.56457835943372503</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -13787,7 +13759,7 @@
         <v>0.73539073670764898</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>71</v>
       </c>
@@ -13837,7 +13809,7 @@
         <v>0.141434270155602</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>71</v>
       </c>
@@ -13887,7 +13859,7 @@
         <v>0.72110486670089902</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>71</v>
       </c>
@@ -13937,7 +13909,7 @@
         <v>1.3302569392546</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>71</v>
       </c>
@@ -13987,7 +13959,7 @@
         <v>2.34367802699022</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>71</v>
       </c>
@@ -14037,7 +14009,7 @@
         <v>0.91280848447528795</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>71</v>
       </c>
@@ -14087,7 +14059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>71</v>
       </c>
@@ -14137,7 +14109,7 @@
         <v>1.12381675670827</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>71</v>
       </c>
@@ -14187,7 +14159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>71</v>
       </c>
@@ -14237,7 +14209,7 @@
         <v>8.5492659429581799E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>71</v>
       </c>
@@ -14287,7 +14259,7 @@
         <v>1.7986960588418299</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>71</v>
       </c>
@@ -14337,7 +14309,7 @@
         <v>5.96626977466541E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="8" t="s">
         <v>71</v>
       </c>
@@ -14387,7 +14359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>71</v>
       </c>
@@ -14437,7 +14409,7 @@
         <v>7.6929421170150603</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>71</v>
       </c>
@@ -14487,7 +14459,7 @@
         <v>5.3366162564236204</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>71</v>
       </c>
@@ -14537,7 +14509,7 @@
         <v>3.8798434388497398</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>71</v>
       </c>
@@ -14587,7 +14559,7 @@
         <v>2.4546724764711199</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>71</v>
       </c>
@@ -14637,7 +14609,7 @@
         <v>1.4676296034890699</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>71</v>
       </c>
@@ -14687,7 +14659,7 @@
         <v>5.7428112583511499</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>71</v>
       </c>
@@ -14737,7 +14709,7 @@
         <v>4.78711646581921</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>71</v>
       </c>
@@ -14787,7 +14759,7 @@
         <v>3.49500406775531</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>71</v>
       </c>
@@ -14837,7 +14809,7 @@
         <v>0.27524219374648201</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>71</v>
       </c>
@@ -14887,7 +14859,7 @@
         <v>1.01150179303793</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>71</v>
       </c>
@@ -14937,7 +14909,7 @@
         <v>8.0801834604421696E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>71</v>
       </c>
@@ -14987,7 +14959,7 @@
         <v>0.61111432821312495</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>71</v>
       </c>
@@ -15037,7 +15009,7 @@
         <v>0.72265369039103899</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>71</v>
       </c>
@@ -15087,7 +15059,7 @@
         <v>1.5541178572999601</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>71</v>
       </c>
@@ -15137,7 +15109,7 @@
         <v>0.95452538170929702</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>71</v>
       </c>
@@ -15187,7 +15159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>71</v>
       </c>
@@ -15237,7 +15209,7 @@
         <v>0.33022948837353999</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>71</v>
       </c>
@@ -15287,7 +15259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>71</v>
       </c>
@@ -15337,7 +15309,7 @@
         <v>2.7351699789180399</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>71</v>
       </c>
@@ -15387,7 +15359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>71</v>
       </c>
@@ -15437,7 +15409,7 @@
         <v>0.14346940232233399</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>71</v>
       </c>
@@ -15487,7 +15459,7 @@
         <v>0.104369910959967</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>71</v>
       </c>
@@ -15537,7 +15509,7 @@
         <v>0.44208205432284597</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="8" t="s">
         <v>71</v>
       </c>
@@ -15587,7 +15559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>71</v>
       </c>
@@ -15637,7 +15609,7 @@
         <v>8.5854829925408502</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>71</v>
       </c>
@@ -15687,7 +15659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>71</v>
       </c>
@@ -15737,7 +15709,7 @@
         <v>3.1623696697645598</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>71</v>
       </c>
@@ -15787,7 +15759,7 @@
         <v>1.09938410979648</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>71</v>
       </c>
@@ -15837,7 +15809,7 @@
         <v>0.72513999528865003</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>71</v>
       </c>
@@ -15887,7 +15859,7 @@
         <v>1.5860341173577399</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>71</v>
       </c>
@@ -15937,7 +15909,7 @@
         <v>1.2588469077050199</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>71</v>
       </c>
@@ -15987,7 +15959,7 @@
         <v>1.8542280757868299</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>71</v>
       </c>
@@ -16037,7 +16009,7 @@
         <v>0.27271660191151698</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>71</v>
       </c>
@@ -16087,7 +16059,7 @@
         <v>0.11626341845905799</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>71</v>
       </c>
@@ -16137,7 +16109,7 @@
         <v>0.15633203537898999</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>71</v>
       </c>
@@ -16187,7 +16159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>71</v>
       </c>
@@ -16237,7 +16209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>71</v>
       </c>
@@ -16287,7 +16259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>71</v>
       </c>
@@ -16337,7 +16309,7 @@
         <v>0.76966923343984806</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>71</v>
       </c>
@@ -16387,7 +16359,7 @@
         <v>7.3875972958818399E-4</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>71</v>
       </c>
@@ -16437,7 +16409,7 @@
         <v>9.9516612044489403E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>71</v>
       </c>
@@ -16487,7 +16459,7 @@
         <v>0.66588455250901701</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>71</v>
       </c>
@@ -16537,7 +16509,7 @@
         <v>0.312368351319814</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>71</v>
       </c>
@@ -16587,7 +16559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>71</v>
       </c>
@@ -16637,7 +16609,7 @@
         <v>0.53459643320253203</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>71</v>
       </c>
@@ -16687,7 +16659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>71</v>
       </c>
@@ -16737,7 +16709,7 @@
         <v>0.25044677481899202</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="8" t="s">
         <v>71</v>
       </c>
@@ -16787,7 +16759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>71</v>
       </c>
@@ -16837,7 +16809,7 @@
         <v>8.6387752630817598</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>71</v>
       </c>
@@ -16887,7 +16859,7 @@
         <v>6.5830645084491604</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>71</v>
       </c>
@@ -16937,7 +16909,7 @@
         <v>2.2285644694330702</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>71</v>
       </c>
@@ -16987,7 +16959,7 @@
         <v>3.5057053033814198</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>71</v>
       </c>
@@ -17037,7 +17009,7 @@
         <v>1.1212669287497301</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>71</v>
       </c>
@@ -17087,7 +17059,7 @@
         <v>5.1390821003929199</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>71</v>
       </c>
@@ -17137,7 +17109,7 @@
         <v>4.7325336070364603</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>71</v>
       </c>
@@ -17187,7 +17159,7 @@
         <v>0.35285328894632401</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>71</v>
       </c>
@@ -17237,7 +17209,7 @@
         <v>0.65752010497073299</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>71</v>
       </c>
@@ -17287,7 +17259,7 @@
         <v>8.3657308661940294E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>71</v>
       </c>
@@ -17337,7 +17309,7 @@
         <v>2.7724359790542701E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>71</v>
       </c>
@@ -17387,7 +17359,7 @@
         <v>0.88723252710895495</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>71</v>
       </c>
@@ -17437,7 +17409,7 @@
         <v>0.45135810300045298</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>71</v>
       </c>
@@ -17487,7 +17459,7 @@
         <v>1.2108225099318699</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>71</v>
       </c>
@@ -17537,7 +17509,7 @@
         <v>1.0117753032524099</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>71</v>
       </c>
@@ -17587,7 +17559,7 @@
         <v>0.40729770016123101</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>71</v>
       </c>
@@ -17637,7 +17609,7 @@
         <v>0.84739401582010099</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>71</v>
       </c>
@@ -17687,7 +17659,7 @@
         <v>0.124348235669486</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>71</v>
       </c>
@@ -17737,7 +17709,7 @@
         <v>0.80351607379834</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>71</v>
       </c>
@@ -17787,7 +17759,7 @@
         <v>1.0130591371504201</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>71</v>
       </c>
@@ -17837,7 +17809,7 @@
         <v>0.415652454858425</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>71</v>
       </c>
@@ -17887,7 +17859,7 @@
         <v>1.7133389701839199</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>71</v>
       </c>
@@ -17937,7 +17909,7 @@
         <v>5.7259390416657903E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" s="8" t="s">
         <v>71</v>
       </c>
@@ -17987,7 +17959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>71</v>
       </c>
@@ -18037,7 +18009,7 @@
         <v>5.9511741172391801</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>71</v>
       </c>
@@ -18087,7 +18059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>71</v>
       </c>
@@ -18137,7 +18109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>71</v>
       </c>
@@ -18187,7 +18159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>71</v>
       </c>
@@ -18237,7 +18209,7 @@
         <v>0.83152000055865605</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>71</v>
       </c>
@@ -18287,7 +18259,7 @@
         <v>1.9698880031496599</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>71</v>
       </c>
@@ -18337,7 +18309,7 @@
         <v>0.37082648428224302</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>71</v>
       </c>
@@ -18387,7 +18359,7 @@
         <v>0.37801395297624701</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>71</v>
       </c>
@@ -18437,7 +18409,7 @@
         <v>2.2043596343463201</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>71</v>
       </c>
@@ -18487,7 +18459,7 @@
         <v>0.60219138138698103</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>71</v>
       </c>
@@ -18537,7 +18509,7 @@
         <v>6.5267434676241798E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>71</v>
       </c>
@@ -18587,7 +18559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>71</v>
       </c>
@@ -18637,7 +18609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>71</v>
       </c>
@@ -18687,7 +18659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>71</v>
       </c>
@@ -18737,7 +18709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>71</v>
       </c>
@@ -18787,7 +18759,7 @@
         <v>0.75380238057940896</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>71</v>
       </c>
@@ -18837,7 +18809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>71</v>
       </c>
@@ -18887,7 +18859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>71</v>
       </c>
@@ -18937,7 +18909,7 @@
         <v>0.122396136426293</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>71</v>
       </c>
@@ -18987,7 +18959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>71</v>
       </c>
@@ -19037,7 +19009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>71</v>
       </c>
@@ -19087,7 +19059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>71</v>
       </c>
@@ -19137,7 +19109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A217" s="8" t="s">
         <v>71</v>
       </c>
@@ -19187,7 +19159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>71</v>
       </c>
@@ -19237,7 +19209,7 @@
         <v>7.7105176699701801</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>71</v>
       </c>
@@ -19287,7 +19259,7 @@
         <v>5.2359066847689499</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>71</v>
       </c>
@@ -19337,7 +19309,7 @@
         <v>3.0220194710718098</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>71</v>
       </c>
@@ -19387,7 +19359,7 @@
         <v>4.1782559223799396</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>71</v>
       </c>
@@ -19437,7 +19409,7 @@
         <v>1.55310582969864</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>71</v>
       </c>
@@ -19487,7 +19459,7 @@
         <v>1.71403071373904</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>71</v>
       </c>
@@ -19537,7 +19509,7 @@
         <v>1.4603853790292201</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>71</v>
       </c>
@@ -19587,7 +19559,7 @@
         <v>0.19385241601293199</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>71</v>
       </c>
@@ -19637,7 +19609,7 @@
         <v>1.6770995745527399</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>71</v>
       </c>
@@ -19687,7 +19659,7 @@
         <v>0.17427739978734</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>71</v>
       </c>
@@ -19737,7 +19709,7 @@
         <v>9.7341090100060798E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>71</v>
       </c>
@@ -19787,7 +19759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>71</v>
       </c>
@@ -19837,7 +19809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>71</v>
       </c>
@@ -19887,7 +19859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>71</v>
       </c>
@@ -19937,7 +19909,7 @@
         <v>1.4440497466333799</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>71</v>
       </c>
@@ -19987,7 +19959,7 @@
         <v>1.1586528409599199</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>71</v>
       </c>
@@ -20037,7 +20009,7 @@
         <v>0.30758807032337399</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>71</v>
       </c>
@@ -20087,7 +20059,7 @@
         <v>0.60383913695979496</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>71</v>
       </c>
@@ -20137,7 +20109,7 @@
         <v>0.79665578059285203</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>71</v>
       </c>
@@ -20187,7 +20159,7 @@
         <v>0.76785835803742797</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>71</v>
       </c>
@@ -20237,7 +20209,7 @@
         <v>0.346711297013511</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>71</v>
       </c>
@@ -20287,7 +20259,7 @@
         <v>0.317312979262035</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>71</v>
       </c>
@@ -20337,7 +20309,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A241" s="8" t="s">
         <v>71</v>
       </c>
